--- a/data_u1/meta_outcome_soe.xlsx
+++ b/data_u1/meta_outcome_soe.xlsx
@@ -1092,7 +1092,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>16.7% of eligible studies and 14.7% of participants had usable data.</t>
+          <t>15.4% of eligible studies and 13.9% of participants had usable data.</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>25% of eligible studies and 25.4% of participants had usable data.</t>
+          <t>23.1% of eligible studies and 24.1% of participants had usable data.</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1280,7 +1280,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>33.3% of eligible studies and 28% of participants had usable data.</t>
+          <t>30.8% of eligible studies and 26.5% of participants had usable data.</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1374,7 +1374,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>33.3% of eligible studies and 28% of participants had usable data.</t>
+          <t>30.8% of eligible studies and 26.5% of participants had usable data.</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1468,7 +1468,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>33.3% of eligible studies and 28% of participants had usable data.</t>
+          <t>30.8% of eligible studies and 26.5% of participants had usable data.</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1562,7 +1562,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>25% of eligible studies and 25.4% of participants had usable data.</t>
+          <t>23.1% of eligible studies and 24.1% of participants had usable data.</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -1797,7 +1797,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>8.3% of eligible studies and 3.8% of participants had usable data.</t>
+          <t>7.7% of eligible studies and 3.6% of participants had usable data.</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -1985,7 +1985,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>8.3% of eligible studies and 10.9% of participants had usable data.</t>
+          <t>7.7% of eligible studies and 10.3% of participants had usable data.</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2079,7 +2079,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>25% of eligible studies and 25.4% of participants had usable data.</t>
+          <t>23.1% of eligible studies and 24.1% of participants had usable data.</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2220,7 +2220,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>8.3% of eligible studies and 10.9% of participants had usable data.</t>
+          <t>7.7% of eligible studies and 10.3% of participants had usable data.</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2314,7 +2314,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>8.3% of eligible studies and 9.8% of participants had usable data.</t>
+          <t>7.7% of eligible studies and 9.3% of participants had usable data.</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -2361,7 +2361,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>16.7% of eligible studies and 14.5% of participants had usable data.</t>
+          <t>15.4% of eligible studies and 13.8% of participants had usable data.</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -2502,7 +2502,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>16.7% of eligible studies and 21.6% of participants had usable data.</t>
+          <t>15.4% of eligible studies and 20.5% of participants had usable data.</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>8.3% of eligible studies and 10.9% of participants had usable data.</t>
+          <t>7.7% of eligible studies and 10.3% of participants had usable data.</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">

--- a/data_u1/meta_outcome_soe.xlsx
+++ b/data_u1/meta_outcome_soe.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I102"/>
+  <dimension ref="A1:I115"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -513,12 +513,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>4 weeks</t>
+          <t>4-6 weeks</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>N=2 n=399; Random-effects: SMD=0.23, 95%CI: 0.03, 0.43; Fixed-effecs: SMD=0.23, 95%CI: 0.03, 0.43</t>
+          <t>N=4 n=1291; Random-effects: SMD=0.13, 95%CI: 0, 0.26; Fixed-effecs: SMD=0.12, 95%CI: 0.01, 0.24</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -528,7 +528,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>40% of eligible studies and 27.7% of participants had usable data.</t>
+          <t>80% of eligible studies and 89.7% of participants had usable data.</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -560,12 +560,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>4 weeks</t>
+          <t>4-6 weeks</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>N=2 n=399; Random-effects: SMD=0.27, 95%CI: -0.06, 0.59; Fixed-effecs: SMD=0.29, 95%CI: 0.09, 0.49</t>
+          <t>N=4 n=1291; Random-effects: SMD=0.15, 95%CI: -0.02, 0.33; Fixed-effecs: SMD=0.14, 95%CI: 0.03, 0.26</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -575,7 +575,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>40% of eligible studies and 27.7% of participants had usable data.</t>
+          <t>80% of eligible studies and 89.7% of participants had usable data.</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>1 study with overall high risk of bias.</t>
+          <t>1 study with an overall low risk of bias.</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -711,7 +711,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>1 study with overall high risk of bias.</t>
+          <t>1 study with an overall low risk of bias.</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -805,7 +805,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>1 study with overall high risk of bias.</t>
+          <t>1 study with an overall low risk of bias.</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -852,7 +852,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>1 study with overall high risk of bias.</t>
+          <t>1 study with an overall low risk of bias.</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1129,7 +1129,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>N=6 n=1423; Random-effects: 23.4% vs. 20%, OR=1.22, 95%CI: 0.93, 1.6; Fixed-effecs: OR=1.23, 95%CI: 0.94, 1.61</t>
+          <t>N=7 n=1451; Random-effects: 23.4% vs. 19.9%, OR=1.23, 95%CI: 0.94, 1.61; Fixed-effecs: OR=1.24, 95%CI: 0.95, 1.62</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>75% of eligible studies and 90.9% of participants had usable data.</t>
+          <t>87.5% of eligible studies and 92.7% of participants had usable data.</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>83.3% studies and 97.3% participants with schizophrenia.</t>
+          <t>71.4% studies and 95.4% participants with schizophrenia.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>N=4 n=524; Random-effects: 8.3% vs. 7.6%, OR=1.1, 95%CI: 0.57, 2.14; Fixed-effecs: OR=1.13, 95%CI: 0.59, 2.17</t>
+          <t>N=7 n=1451; Random-effects: 9.8% vs. 6.4%, OR=1.57, 95%CI: 1.02, 2.42; Fixed-effecs: OR=1.62, 95%CI: 1.06, 2.47</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1233,12 +1233,12 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>50% of eligible studies and 33.5% of participants had usable data.</t>
+          <t>87.5% of eligible studies and 92.7% of participants had usable data.</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>75% studies and 92.6% participants with schizophrenia.</t>
+          <t>71.4% studies and 95.4% participants with schizophrenia.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1317,7 +1317,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>N=4 n=524; Random-effects: 44.6% vs. 51.1%, OR=0.77, 95%CI: 0.53, 1.12; Fixed-effecs: OR=0.77, 95%CI: 0.53, 1.11</t>
+          <t>N=7 n=1451; Random-effects: 42% vs. 38.9%, OR=1.14, 95%CI: 0.8, 1.63; Fixed-effecs: OR=1.21, 95%CI: 0.96, 1.52</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1327,12 +1327,12 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>50% of eligible studies and 33.5% of participants had usable data.</t>
+          <t>87.5% of eligible studies and 92.7% of participants had usable data.</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>75% studies and 92.6% participants with schizophrenia.</t>
+          <t>71.4% studies and 95.4% participants with schizophrenia.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1411,7 +1411,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>N=4 n=524; Random-effects: 3.2% vs. 2.8%, OR=1.16, 95%CI: 0.36, 3.74; Fixed-effecs: OR=1.21, 95%CI: 0.41, 3.54</t>
+          <t>N=7 n=1451; Random-effects: 5.8% vs. 4.5%, OR=1.31, 95%CI: 0.74, 2.32; Fixed-effecs: OR=1.35, 95%CI: 0.82, 2.24</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1421,12 +1421,12 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>50% of eligible studies and 33.5% of participants had usable data.</t>
+          <t>87.5% of eligible studies and 92.7% of participants had usable data.</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>75% studies and 92.6% participants with schizophrenia.</t>
+          <t>71.4% studies and 95.4% participants with schizophrenia.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1505,7 +1505,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>N=4 n=524; 3.9% vs. 1.3%, OR=3.15, 95%CI: 0.13, 78.11</t>
+          <t>N=7 n=1451; 3.2% vs. 1%, OR=3.15, 95%CI: 0.13, 78.11</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1515,12 +1515,12 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>50% of eligible studies and 33.5% of participants had usable data.</t>
+          <t>87.5% of eligible studies and 92.7% of participants had usable data.</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>75% studies and 92.6% participants with schizophrenia.</t>
+          <t>71.4% studies and 95.4% participants with schizophrenia.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -1599,7 +1599,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>N=4 n=524; Random-effects: 5% vs. 4.4%, OR=1.15, 95%CI: 0.34, 3.88; Fixed-effecs: OR=1.14, 95%CI: 0.5, 2.64</t>
+          <t>N=6 n=987; Random-effects: 6.3% vs. 5.7%, OR=1.1, 95%CI: 0.62, 1.95; Fixed-effecs: OR=1.16, 95%CI: 0.66, 2.02</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1609,12 +1609,12 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>50% of eligible studies and 33.5% of participants had usable data.</t>
+          <t>75% of eligible studies and 63.1% of participants had usable data.</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>75% studies and 92.6% participants with schizophrenia.</t>
+          <t>66.7% studies and 93.2% participants with schizophrenia.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -1829,22 +1829,22 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>4 weeks</t>
+          <t>4-6 weeks</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>N=1 n=245; 3.3% vs. 3.2%, OR=1.04, 95%CI: 0.25, 4.27</t>
+          <t>N=3 n=1144; Random-effects: 2.9% vs. 2.8%, OR=1.02, 95%CI: 0.49, 2.12; Fixed-effecs: OR=1.02, 95%CI: 0.49, 2.12</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>1 study with an overall low risk of bias.</t>
+          <t xml:space="preserve"> All studies had overall low risk of bias.</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>12.5% of eligible studies and 15.7% of participants had usable data.</t>
+          <t>37.5% of eligible studies and 73.1% of participants had usable data.</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -1923,12 +1923,12 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>4 weeks</t>
+          <t>4-6 weeks</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>N=2 n=458; Random-effects: 5.5% vs. 4.2%, OR=1.35, 95%CI: 0.53, 3.43; Fixed-effecs: OR=1.38, 95%CI: 0.56, 3.45</t>
+          <t>N=5 n=1385; Random-effects: 5.5% vs. 4.7%, OR=1.19, 95%CI: 0.71, 1.99; Fixed-effecs: OR=1.22, 95%CI: 0.73, 2.04</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1938,12 +1938,12 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>25% of eligible studies and 29.3% of participants had usable data.</t>
+          <t>62.5% of eligible studies and 88.5% of participants had usable data.</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>No clear indication of indirectness.</t>
+          <t>80% studies and 98% participants with schizophrenia.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -2017,12 +2017,12 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>4 weeks</t>
+          <t>4-6 weeks</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>N=2 n=458; Random-effects: 2.6% vs. 7.6%, OR=0.32, 95%CI: 0.12, 0.85; Fixed-effecs: OR=0.31, 95%CI: 0.12, 0.8</t>
+          <t>N=5 n=1385; Random-effects: 5.2% vs. 5.8%, OR=0.89, 95%CI: 0.3, 2.64; Fixed-effecs: OR=1.17, 95%CI: 0.73, 1.89</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -2032,12 +2032,12 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>25% of eligible studies and 29.3% of participants had usable data.</t>
+          <t>62.5% of eligible studies and 88.5% of participants had usable data.</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>No clear indication of indirectness.</t>
+          <t>80% studies and 98% participants with schizophrenia.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -2116,7 +2116,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>N=3 n=311; Random-effects: 7.1% vs. 6.3%, OR=1.14, 95%CI: 0.44, 3; Fixed-effecs: OR=1.15, 95%CI: 0.44, 2.99</t>
+          <t>N=5 n=774; Random-effects: 5.5% vs. 4.7%, OR=1.18, 95%CI: 0.47, 2.99; Fixed-effecs: OR=1.24, 95%CI: 0.48, 3.18</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -2126,12 +2126,12 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>37.5% of eligible studies and 19.9% of participants had usable data.</t>
+          <t>62.5% of eligible studies and 49.5% of participants had usable data.</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>66.7% studies and 87.5% participants with schizophrenia.</t>
+          <t>60% studies and 91.3% participants with schizophrenia.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -2163,7 +2163,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>N=4 n=524; Random-effects: 7.6% vs. 6.7%, OR=1.13, 95%CI: 0.27, 4.66; Fixed-effecs: OR=0.81, 95%CI: 0.38, 1.69</t>
+          <t>N=7 n=1451; Random-effects: 8.5% vs. 7.4%, OR=1.16, 95%CI: 0.57, 2.34; Fixed-effecs: OR=1.15, 95%CI: 0.75, 1.76</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>50% of eligible studies and 33.5% of participants had usable data.</t>
+          <t>87.5% of eligible studies and 92.7% of participants had usable data.</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>75% studies and 92.6% participants with schizophrenia.</t>
+          <t>71.4% studies and 95.4% participants with schizophrenia.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -2257,7 +2257,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>N=3 n=485; Random-effects: 7.3% vs. 8.4%, OR=0.86, 95%CI: 0.43, 1.69; Fixed-effecs: OR=0.86, 95%CI: 0.44, 1.68</t>
+          <t>N=6 n=1412; Random-effects: 10.7% vs. 8.5%, OR=1.29, 95%CI: 0.86, 1.95; Fixed-effecs: OR=1.32, 95%CI: 0.89, 1.94</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -2267,12 +2267,12 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>37.5% of eligible studies and 31% of participants had usable data.</t>
+          <t>75% of eligible studies and 90.2% of participants had usable data.</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>No clear indication of indirectness.</t>
+          <t>83.3% studies and 98% participants with schizophrenia.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -2539,7 +2539,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>N=2 n=66; 12.4% vs. 5.4%, OR=2.48, 95%CI: 0.25, 24.65</t>
+          <t>N=4 n=529; Random-effects: 6.2% vs. 2.9%, OR=2.23, 95%CI: 0.34, 14.68; Fixed-effecs: OR=3.14, 95%CI: 0.33, 29.62</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2549,12 +2549,12 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>25% of eligible studies and 4.2% of participants had usable data.</t>
+          <t>50% of eligible studies and 33.8% of participants had usable data.</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>50% studies and 40.9% participants with schizophrenia.</t>
+          <t>50% studies and 87.3% participants with schizophrenia.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -2628,27 +2628,27 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>12 weeks</t>
+          <t>6-12 weeks</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>N=1 n=27; 11.5% vs. 3.1%, OR=4.04, 95%CI: 0.15, 108.57</t>
+          <t>N=3 n=490; Random-effects: 3.3% vs. 2.6%, OR=1.28, 95%CI: 0.15, 11.23; Fixed-effecs: OR=1.44, 95%CI: 0.14, 15.03</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>1 study with an overall low risk of bias.</t>
+          <t xml:space="preserve"> All studies had overall low risk of bias.</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>12.5% of eligible studies and 1.7% of participants had usable data.</t>
+          <t>37.5% of eligible studies and 31.3% of participants had usable data.</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>No clear indication of indirectness.</t>
+          <t>66.7% studies and 94.3% participants with schizophrenia.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -2660,42 +2660,42 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>TAAR1 agonists vs. antipsychotics in adults with an acute episode of schizophrenia</t>
+          <t>TAAR1 agonists vs. placebo in any eligible population</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>efficacy</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Overall symptoms</t>
+          <t>Worsening or exacerbation of schizophrenia</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>4 weeks</t>
+          <t>4-12 weeks</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>N=1 n=156; SMD=-0.53, 95%CI: -0.86, -0.2</t>
+          <t>N=6 n=1412; Random-effects: 6.5% vs. 4.4%, OR=1.49, 95%CI: 0.73, 3.08; Fixed-effecs: OR=1.78, 95%CI: 1.07, 2.95</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>1 study with an overall low risk of bias.</t>
+          <t xml:space="preserve"> All studies had overall low risk of bias.</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>1 eligible study with usable data.</t>
+          <t>75% of eligible studies and 90.2% of participants had usable data.</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>No clear indication of indirectness.</t>
+          <t>83.3% studies and 98% participants with schizophrenia.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -2717,7 +2717,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Response to treatment</t>
+          <t>Overall symptoms</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -2727,7 +2727,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>N=1 n=214; 7.9% vs. 13.5%, OR=0.55, 95%CI: 0.22, 1.35</t>
+          <t>N=1 n=156; SMD=-0.53, 95%CI: -0.86, -0.2</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2764,7 +2764,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Positive symptoms</t>
+          <t>Response to treatment</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -2774,7 +2774,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>N=1 n=156; SMD=-0.55, 95%CI: -0.89, -0.22</t>
+          <t>N=1 n=214; 7.9% vs. 13.5%, OR=0.55, 95%CI: 0.22, 1.35</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2811,7 +2811,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Negative symptoms</t>
+          <t>Positive symptoms</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -2821,7 +2821,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>N=1 n=156; SMD=-0.13, 95%CI: -0.46, 0.19</t>
+          <t>N=1 n=156; SMD=-0.55, 95%CI: -0.89, -0.22</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2858,7 +2858,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Depressive symptoms</t>
+          <t>Negative symptoms</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -2868,7 +2868,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>N=1 n=156; SMD=-0.23, 95%CI: -0.56, 0.1</t>
+          <t>N=1 n=156; SMD=-0.13, 95%CI: -0.46, 0.19</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2895,7 +2895,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>TAAR1 agonists vs. antipsychotics in adults with clinically stable schizophrenia</t>
+          <t>TAAR1 agonists vs. antipsychotics in adults with an acute episode of schizophrenia</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2905,22 +2905,22 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Relapse</t>
+          <t>Depressive symptoms</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>52 weeks</t>
+          <t>4 weeks</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>N=1 n=303; 14.4% vs. 5.9%, OR=2.7, 95%CI: 1.08, 6.73</t>
+          <t>N=1 n=156; SMD=-0.23, 95%CI: -0.56, 0.1</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>1 study with overall high risk of bias.</t>
+          <t>1 study with an overall low risk of bias.</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -2942,27 +2942,27 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>TAAR1 agonists vs. antipsychotics in any eligible population</t>
+          <t>TAAR1 agonists vs. antipsychotics in adults with clinically stable schizophrenia</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>efficacy</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Dropouts due to any reason</t>
+          <t>Overall symptoms</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>1 day</t>
+          <t>52 weeks</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>N=1 n=71; 14.3% vs. 5.6%, OR=2.83, 95%CI: 0.51, 15.69</t>
+          <t>N=1 n=303; SMD=-0.13, 95%CI: -0.37, 0.11</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2972,12 +2972,12 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>50% of eligible studies and 70.3% of participants had usable data.</t>
+          <t>1 eligible study with usable data.</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>0% studies and 0% participants with schizophrenia.</t>
+          <t>No clear indication of indirectness.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -2989,37 +2989,37 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>TAAR1 agonists vs. antipsychotics in any eligible population</t>
+          <t>TAAR1 agonists vs. antipsychotics in adults with clinically stable schizophrenia</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>efficacy</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Dropouts due to any reason</t>
+          <t>Relapse</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>4 weeks</t>
+          <t>52 weeks</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>N=1 n=214; 22.9% vs. 18.9%, OR=1.27, 95%CI: 0.63, 2.56</t>
+          <t>N=1 n=303; 3% vs. 2%, OR=1.54, 95%CI: 0.3, 7.76</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>1 study with an overall low risk of bias.</t>
+          <t>1 study with overall high risk of bias.</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>50% of eligible studies and 91.8% of participants had usable data.</t>
+          <t>1 eligible study with usable data.</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -3051,12 +3051,12 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>52 weeks</t>
+          <t>1 day</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>N=1 n=303; 47.8% vs. 44.1%, OR=1.16, 95%CI: 0.72, 1.87</t>
+          <t>N=1 n=71; 14.3% vs. 5.6%, OR=2.83, 95%CI: 0.51, 15.69</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -3066,12 +3066,12 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>1 eligible study with usable data.</t>
+          <t>50% of eligible studies and 70.3% of participants had usable data.</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>No clear indication of indirectness.</t>
+          <t>0% studies and 0% participants with schizophrenia.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -3093,17 +3093,17 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Dropouts due to adverse events</t>
+          <t>Dropouts due to any reason</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>1 day</t>
+          <t>4 weeks</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>N=1 n=71; not estimable effect size 0 events in both arms</t>
+          <t>N=1 n=214; 22.9% vs. 18.9%, OR=1.27, 95%CI: 0.63, 2.56</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -3113,12 +3113,12 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>50% of eligible studies and 70.3% of participants had usable data.</t>
+          <t>50% of eligible studies and 91.8% of participants had usable data.</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>0% studies and 0% participants with schizophrenia.</t>
+          <t>No clear indication of indirectness.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -3140,17 +3140,17 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Dropouts due to adverse events</t>
+          <t>Dropouts due to any reason</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>4 weeks</t>
+          <t>52 weeks</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>N=1 n=214; 6.4% vs. 1.4%, OR=5.02, 95%CI: 0.62, 40.38</t>
+          <t>N=1 n=303; 47.8% vs. 44.1%, OR=1.16, 95%CI: 0.72, 1.87</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -3160,7 +3160,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>50% of eligible studies and 91.8% of participants had usable data.</t>
+          <t>1 eligible study with usable data.</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -3192,12 +3192,12 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>52 weeks</t>
+          <t>1 day</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>N=1 n=303; 21.9% vs. 20.6%, OR=1.08, 95%CI: 0.6, 1.94</t>
+          <t>N=1 n=71; not estimable effect size 0 events in both arms</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -3207,12 +3207,12 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>1 eligible study with usable data.</t>
+          <t>50% of eligible studies and 70.3% of participants had usable data.</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>No clear indication of indirectness.</t>
+          <t>0% studies and 0% participants with schizophrenia.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -3234,32 +3234,32 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Any adverse event</t>
+          <t>Dropouts due to adverse events</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>1 day</t>
+          <t>4 weeks</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>N=2 n=133; Random-effects: 87.2% vs. 36%, OR=12.17, 95%CI: 1.22, 121.04; Fixed-effecs: OR=9.49, 95%CI: 3.94, 22.84</t>
+          <t>N=1 n=214; 6.4% vs. 1.4%, OR=5.02, 95%CI: 0.62, 40.38</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>50% had overall low risk of bias</t>
+          <t>1 study with an overall low risk of bias.</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>All eligible studies had usable data.</t>
+          <t>50% of eligible studies and 91.8% of participants had usable data.</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>50% studies and 46.6% participants with schizophrenia.</t>
+          <t>No clear indication of indirectness.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -3281,17 +3281,17 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Any adverse event</t>
+          <t>Dropouts due to adverse events</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>4 weeks</t>
+          <t>52 weeks</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>N=1 n=214; 26.5% vs. 48.6%, OR=0.38, 95%CI: 0.21, 0.68</t>
+          <t>N=1 n=303; 23.9% vs. 20.6%, OR=1.21, 95%CI: 0.68, 2.16</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -3301,7 +3301,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>50% of eligible studies and 91.8% of participants had usable data.</t>
+          <t>1 eligible study with usable data.</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -3328,7 +3328,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Serious adverse events</t>
+          <t>Any adverse event</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -3338,7 +3338,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>N=2 n=133; 4.5% vs. 1.5%, OR=3.17, 95%CI: 0.13, 80.58</t>
+          <t>N=2 n=133; Random-effects: 87.2% vs. 36%, OR=12.17, 95%CI: 1.22, 121.04; Fixed-effecs: OR=9.49, 95%CI: 3.94, 22.84</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -3375,7 +3375,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Serious adverse events</t>
+          <t>Any adverse event</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -3385,7 +3385,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>N=1 n=214; 2.5% vs. 0.7%, OR=3.79, 95%CI: 0.19, 74.42</t>
+          <t>N=1 n=214; 26.5% vs. 48.6%, OR=0.38, 95%CI: 0.21, 0.68</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -3422,32 +3422,32 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Mortality due to any cause</t>
+          <t>Any adverse event</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>1 day</t>
+          <t>52 weeks</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>N=2 n=133; not estimable effect size 0 events in both arms</t>
+          <t>N=1 n=303; 76% vs. 75.5%, OR=1.03, 95%CI: 0.59, 1.8</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>50% had overall low risk of bias</t>
+          <t>1 study with an overall low risk of bias.</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>All eligible studies had usable data.</t>
+          <t>1 eligible study with usable data.</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>50% studies and 46.6% participants with schizophrenia.</t>
+          <t>No clear indication of indirectness.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -3469,32 +3469,32 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Mortality due to any cause</t>
+          <t>Serious adverse events</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>4 weeks</t>
+          <t>1 day</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>N=1 n=214; not estimable effect size 0 events in both arms</t>
+          <t>N=2 n=133; 4.5% vs. 1.5%, OR=3.17, 95%CI: 0.13, 80.58</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>1 study with an overall low risk of bias.</t>
+          <t>50% had overall low risk of bias</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>50% of eligible studies and 91.8% of participants had usable data.</t>
+          <t>All eligible studies had usable data.</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>No clear indication of indirectness.</t>
+          <t>50% studies and 46.6% participants with schizophrenia.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -3516,32 +3516,32 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Nausea/vomitting</t>
+          <t>Serious adverse events</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>1 day</t>
+          <t>4 weeks</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>N=2 n=133; Random-effects: 30.5% vs. 1.5%, OR=29.82, 95%CI: 3.87, 229.8; Fixed-effecs: OR=30.28, 95%CI: 3.95, 231.96</t>
+          <t>N=1 n=214; 2.5% vs. 0.7%, OR=3.79, 95%CI: 0.19, 74.42</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>50% had overall low risk of bias</t>
+          <t>1 study with an overall low risk of bias.</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>All eligible studies had usable data.</t>
+          <t>50% of eligible studies and 91.8% of participants had usable data.</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>50% studies and 46.6% participants with schizophrenia.</t>
+          <t>No clear indication of indirectness.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -3563,17 +3563,17 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Nausea/vomitting</t>
+          <t>Serious adverse events</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>4 weeks</t>
+          <t>52 weeks</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>N=1 n=214; 1.4% vs. 8.1%, OR=0.16, 95%CI: 0.03, 0.84</t>
+          <t>N=1 n=303; 8.2% vs. 0.5%, OR=18.23, 95%CI: 1.08, 307.1</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -3583,7 +3583,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>50% of eligible studies and 91.8% of participants had usable data.</t>
+          <t>1 eligible study with usable data.</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -3610,32 +3610,32 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Weight (kg)</t>
+          <t>Mortality due to any cause</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>52 weeks</t>
+          <t>1 day</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>N=1 n=303; MD=-2.6, 95%CI: -4.12, -1.08</t>
+          <t>N=2 n=133; not estimable effect size 0 events in both arms</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>1 study with an overall low risk of bias.</t>
+          <t>50% had overall low risk of bias</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>1 eligible study with usable data.</t>
+          <t>All eligible studies had usable data.</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>No clear indication of indirectness.</t>
+          <t>50% studies and 46.6% participants with schizophrenia.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -3657,7 +3657,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Weight increased (≥7% increase or any cutoff)</t>
+          <t>Mortality due to any cause</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -3667,7 +3667,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>N=1 n=214; 1.4% vs. 10.8%, OR=0.12, 95%CI: 0.02, 0.58</t>
+          <t>N=1 n=214; not estimable effect size 0 events in both arms</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -3704,7 +3704,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Weight increased (≥7% increase or any cutoff)</t>
+          <t>Mortality due to any cause</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -3714,7 +3714,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>N=1 n=303; 3.9% vs. 10.8%, OR=0.34, 95%CI: 0.13, 0.88</t>
+          <t>N=1 n=303; not estimable effect size 0 events in both arms</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -3751,32 +3751,32 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Agitation</t>
+          <t>Nausea/vomitting</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>4 weeks</t>
+          <t>1 day</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>N=1 n=214; 6% vs. 0.7%, OR=9.56, 95%CI: 0.54, 167.96</t>
+          <t>N=2 n=133; Random-effects: 30.5% vs. 1.5%, OR=29.82, 95%CI: 3.87, 229.8; Fixed-effecs: OR=Inf, 95%CI: NaN, NaN</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>1 study with an overall low risk of bias.</t>
+          <t>50% had overall low risk of bias</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>50% of eligible studies and 91.8% of participants had usable data.</t>
+          <t>All eligible studies had usable data.</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>No clear indication of indirectness.</t>
+          <t>50% studies and 46.6% participants with schizophrenia.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -3798,17 +3798,17 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Anxiety</t>
+          <t>Nausea/vomitting</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>1 day</t>
+          <t>4 weeks</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>N=1 n=71; 1.2% vs. 8.3%, OR=0.13, 95%CI: 0.01, 2.71</t>
+          <t>N=1 n=214; 1.4% vs. 8.1%, OR=0.16, 95%CI: 0.03, 0.84</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3818,12 +3818,12 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>50% of eligible studies and 70.3% of participants had usable data.</t>
+          <t>50% of eligible studies and 91.8% of participants had usable data.</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>0% studies and 0% participants with schizophrenia.</t>
+          <t>No clear indication of indirectness.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -3845,17 +3845,17 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Anxiety</t>
+          <t>Nausea/vomitting</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>4 weeks</t>
+          <t>52 weeks</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>N=1 n=214; 3.6% vs. 6.8%, OR=0.51, 95%CI: 0.14, 1.83</t>
+          <t>N=1 n=303; 6.5% vs. 3.9%, OR=1.69, 95%CI: 0.54, 5.33</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3865,7 +3865,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>50% of eligible studies and 91.8% of participants had usable data.</t>
+          <t>1 eligible study with usable data.</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -3892,7 +3892,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Anxiety</t>
+          <t>Weight (kg)</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -3902,7 +3902,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>N=1 n=303; 13.9% vs. 9.8%, OR=1.49, 95%CI: 0.69, 3.2</t>
+          <t>N=1 n=303; MD=-2.6, 95%CI: -4.12, -1.08</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3939,32 +3939,32 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Sedation</t>
+          <t>Weight increased (≥7% increase or any cutoff)</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>1 day</t>
+          <t>4 weeks</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>N=2 n=133; Random-effects: 42.9% vs. 8.6%, OR=7.96, 95%CI: 2.84, 22.36; Fixed-effecs: OR=7.81, 95%CI: 2.76, 22.09</t>
+          <t>N=1 n=214; 1.4% vs. 10.8%, OR=0.12, 95%CI: 0.02, 0.58</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>50% had overall low risk of bias</t>
+          <t>1 study with an overall low risk of bias.</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>All eligible studies had usable data.</t>
+          <t>50% of eligible studies and 91.8% of participants had usable data.</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>50% studies and 46.6% participants with schizophrenia.</t>
+          <t>No clear indication of indirectness.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Sedation</t>
+          <t>Weight increased (≥7% increase or any cutoff)</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -3996,7 +3996,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>N=1 n=303; 5.9% vs. 20.6%, OR=0.24, 95%CI: 0.12, 0.52</t>
+          <t>N=1 n=303; 4.5% vs. 10.8%, OR=0.39, 95%CI: 0.16, 0.97</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -4033,17 +4033,17 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Insomnia</t>
+          <t>Prolactin levels (ng/ml)</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>4 weeks</t>
+          <t>52 weeks</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>N=1 n=214; 5.7% vs. 6.8%, OR=0.84, 95%CI: 0.26, 2.65</t>
+          <t>N=1 n=303; MD=-2.5, 95%CI: -8.26, 3.26</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -4053,7 +4053,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>50% of eligible studies and 91.8% of participants had usable data.</t>
+          <t>1 eligible study with usable data.</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -4080,7 +4080,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Insomnia</t>
+          <t>Akathisia</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -4090,7 +4090,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>N=1 n=303; 14.9% vs. 10.8%, OR=1.45, 95%CI: 0.7, 3.03</t>
+          <t>N=1 n=303; 7% vs. 2%, OR=3.74, 95%CI: 0.83, 16.8</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -4127,17 +4127,17 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Headache</t>
+          <t>Agitation</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>1 day</t>
+          <t>4 weeks</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>N=1 n=71; 11.4% vs. 2.8%, OR=4.52, 95%CI: 0.48, 42.59</t>
+          <t>N=1 n=214; 6% vs. 0.7%, OR=9.56, 95%CI: 0.54, 167.96</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -4147,12 +4147,12 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>50% of eligible studies and 70.3% of participants had usable data.</t>
+          <t>50% of eligible studies and 91.8% of participants had usable data.</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>0% studies and 0% participants with schizophrenia.</t>
+          <t>No clear indication of indirectness.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -4174,17 +4174,17 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Headache</t>
+          <t>Anxiety</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>4 weeks</t>
+          <t>1 day</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>N=1 n=214; 6.4% vs. 8.1%, OR=0.78, 95%CI: 0.27, 2.28</t>
+          <t>N=1 n=71; 1.2% vs. 8.3%, OR=0.13, 95%CI: 0.01, 2.71</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -4194,12 +4194,12 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>50% of eligible studies and 91.8% of participants had usable data.</t>
+          <t>50% of eligible studies and 70.3% of participants had usable data.</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>No clear indication of indirectness.</t>
+          <t>0% studies and 0% participants with schizophrenia.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -4221,27 +4221,27 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>QTc prolongation (any cutoff)</t>
+          <t>Anxiety</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>1 day</t>
+          <t>4 weeks</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>N=1 n=62; not estimable effect size 0 events in both arms</t>
+          <t>N=1 n=214; 3.6% vs. 6.8%, OR=0.51, 95%CI: 0.14, 1.83</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>1 study with overall some concerns in risk of bias.</t>
+          <t>1 study with an overall low risk of bias.</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>50% of eligible studies and 61.4% of participants had usable data.</t>
+          <t>50% of eligible studies and 91.8% of participants had usable data.</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -4268,32 +4268,32 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Dizziness</t>
+          <t>Anxiety</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>1 day</t>
+          <t>52 weeks</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>N=2 n=133; Random-effects: 22.8% vs. 2.3%, OR=12.62, 95%CI: 2.25, 70.79; Fixed-effecs: OR=12.6, 95%CI: 2.25, 70.72</t>
+          <t>N=1 n=303; 13.5% vs. 9.8%, OR=1.43, 95%CI: 0.66, 3.08</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>50% had overall low risk of bias</t>
+          <t>1 study with an overall low risk of bias.</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>All eligible studies had usable data.</t>
+          <t>1 eligible study with usable data.</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>50% studies and 46.6% participants with schizophrenia.</t>
+          <t>No clear indication of indirectness.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -4315,7 +4315,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Anticholinergic symptom</t>
+          <t>Sedation</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -4325,22 +4325,22 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>N=1 n=71; 15.3% vs. 1.4%, OR=13.16, 95%CI: 0.7, 247.71</t>
+          <t>N=2 n=133; Random-effects: 42.9% vs. 8.6%, OR=7.96, 95%CI: 2.84, 22.36; Fixed-effecs: OR=7.81, 95%CI: 2.76, 22.09</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>1 study with an overall low risk of bias.</t>
+          <t>50% had overall low risk of bias</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>50% of eligible studies and 70.3% of participants had usable data.</t>
+          <t>All eligible studies had usable data.</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>0% studies and 0% participants with schizophrenia.</t>
+          <t>50% studies and 46.6% participants with schizophrenia.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -4362,7 +4362,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Anticholinergic symptom</t>
+          <t>Sedation</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -4372,7 +4372,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>N=1 n=303; 3.5% vs. 11.8%, OR=0.27, 95%CI: 0.1, 0.71</t>
+          <t>N=1 n=303; 5.9% vs. 20.6%, OR=0.24, 95%CI: 0.12, 0.52</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -4399,37 +4399,37 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>TAAR1 agonists vs. placebo (addon) in adults with schizophrenia and predominant negative symptoms</t>
+          <t>TAAR1 agonists vs. antipsychotics in any eligible population</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>efficacy</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Overall symptoms</t>
+          <t>Insomnia</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>12 weeks</t>
+          <t>4 weeks</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>N=1 n=76; SMD=0.26, 95%CI: -0.2, 0.72</t>
+          <t>N=1 n=214; 5.7% vs. 6.8%, OR=0.84, 95%CI: 0.26, 2.65</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>1 study with overall high risk of bias.</t>
+          <t>1 study with an overall low risk of bias.</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>1 eligible study with usable data.</t>
+          <t>50% of eligible studies and 91.8% of participants had usable data.</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -4446,32 +4446,32 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>TAAR1 agonists vs. placebo (addon) in adults with schizophrenia and predominant negative symptoms</t>
+          <t>TAAR1 agonists vs. antipsychotics in any eligible population</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>efficacy</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Response to treatment</t>
+          <t>Insomnia</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>12 weeks</t>
+          <t>52 weeks</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>N=1 n=104; 10.4% vs. 10.8%, OR=0.96, 95%CI: 0.26, 3.53</t>
+          <t>N=1 n=303; 14.9% vs. 10.8%, OR=1.45, 95%CI: 0.7, 3.03</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>1 study with overall high risk of bias.</t>
+          <t>1 study with an overall low risk of bias.</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
@@ -4493,27 +4493,27 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>TAAR1 agonists vs. placebo (addon) in adults with schizophrenia and predominant negative symptoms</t>
+          <t>TAAR1 agonists vs. antipsychotics in any eligible population</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>efficacy</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Relapse</t>
+          <t>Headache</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>12 weeks</t>
+          <t>1 day</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>N=1 n=104; not estimable effect size 0 events in both arms</t>
+          <t>N=1 n=71; 11.4% vs. 2.8%, OR=4.52, 95%CI: 0.48, 42.59</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -4523,12 +4523,12 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>1 eligible study with usable data.</t>
+          <t>50% of eligible studies and 70.3% of participants had usable data.</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>No clear indication of indirectness.</t>
+          <t>0% studies and 0% participants with schizophrenia.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -4540,37 +4540,37 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>TAAR1 agonists vs. placebo (addon) in adults with schizophrenia and predominant negative symptoms</t>
+          <t>TAAR1 agonists vs. antipsychotics in any eligible population</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>efficacy</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Positive symptoms</t>
+          <t>Headache</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>12 weeks</t>
+          <t>4 weeks</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>N=1 n=76; SMD=0.18, 95%CI: -0.28, 0.64</t>
+          <t>N=1 n=214; 6.4% vs. 8.1%, OR=0.78, 95%CI: 0.27, 2.28</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>1 study with overall high risk of bias.</t>
+          <t>1 study with an overall low risk of bias.</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>1 eligible study with usable data.</t>
+          <t>50% of eligible studies and 91.8% of participants had usable data.</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -4587,32 +4587,32 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>TAAR1 agonists vs. placebo (addon) in adults with schizophrenia and predominant negative symptoms</t>
+          <t>TAAR1 agonists vs. antipsychotics in any eligible population</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>efficacy</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Negative symptoms</t>
+          <t>Headache</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>12 weeks</t>
+          <t>52 weeks</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>N=1 n=75; SMD=0.25, 95%CI: -0.22, 0.71</t>
+          <t>N=1 n=303; 10% vs. 7.8%, OR=1.3, 95%CI: 0.55, 3.06</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>1 study with overall high risk of bias.</t>
+          <t>1 study with an overall low risk of bias.</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
@@ -4634,7 +4634,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>TAAR1 agonists vs. placebo (addon) in any eligible population</t>
+          <t>TAAR1 agonists vs. antipsychotics in any eligible population</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -4644,27 +4644,27 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Dropouts due to any reason</t>
+          <t>QTc prolongation (any cutoff)</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>12 weeks</t>
+          <t>1 day</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>N=1 n=104; 8.9% vs. 10.8%, OR=0.81, 95%CI: 0.21, 3.08</t>
+          <t>N=1 n=62; not estimable effect size 0 events in both arms</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>1 study with an overall low risk of bias.</t>
+          <t>1 study with overall some concerns in risk of bias.</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>1 eligible study with usable data.</t>
+          <t>50% of eligible studies and 61.4% of participants had usable data.</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -4681,7 +4681,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>TAAR1 agonists vs. placebo (addon) in any eligible population</t>
+          <t>TAAR1 agonists vs. antipsychotics in any eligible population</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -4691,32 +4691,32 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Dropouts due to adverse events</t>
+          <t>Dizziness</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>12 weeks</t>
+          <t>1 day</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>N=1 n=104; 2.2% vs. 1.3%, OR=1.69, 95%CI: 0.07, 42.58</t>
+          <t>N=2 n=133; Random-effects: 22.8% vs. 2.3%, OR=12.62, 95%CI: 2.25, 70.79; Fixed-effecs: OR=19.68, 95%CI: 2.39, 162.25</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>1 study with an overall low risk of bias.</t>
+          <t>50% had overall low risk of bias</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>1 eligible study with usable data.</t>
+          <t>All eligible studies had usable data.</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>No clear indication of indirectness.</t>
+          <t>50% studies and 46.6% participants with schizophrenia.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -4728,7 +4728,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>TAAR1 agonists vs. placebo (addon) in any eligible population</t>
+          <t>TAAR1 agonists vs. antipsychotics in any eligible population</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -4738,17 +4738,17 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Any adverse event</t>
+          <t>Dizziness</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>12 weeks</t>
+          <t>52 weeks</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>N=1 n=104; 20.9% vs. 24.3%, OR=0.82, 95%CI: 0.32, 2.13</t>
+          <t>N=1 n=303; 8% vs. 4.9%, OR=1.68, 95%CI: 0.6, 4.72</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -4775,7 +4775,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>TAAR1 agonists vs. placebo (addon) in any eligible population</t>
+          <t>TAAR1 agonists vs. antipsychotics in any eligible population</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -4785,17 +4785,17 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Serious adverse events</t>
+          <t>Anticholinergic symptom</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>12 weeks</t>
+          <t>1 day</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>N=1 n=104; 3% vs. 2.7%, OR=1.11, 95%CI: 0.1, 12.64</t>
+          <t>N=1 n=71; 15.3% vs. 1.4%, OR=13.16, 95%CI: 0.7, 247.71</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -4805,12 +4805,12 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>1 eligible study with usable data.</t>
+          <t>50% of eligible studies and 70.3% of participants had usable data.</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>No clear indication of indirectness.</t>
+          <t>0% studies and 0% participants with schizophrenia.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -4822,7 +4822,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>TAAR1 agonists vs. placebo (addon) in any eligible population</t>
+          <t>TAAR1 agonists vs. antipsychotics in any eligible population</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -4832,17 +4832,17 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Mortality due to any cause</t>
+          <t>Anticholinergic symptom</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>12 weeks</t>
+          <t>52 weeks</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>N=1 n=104; 0.5% vs. 2.7%, OR=0.18, 95%CI: 0.01, 4.54</t>
+          <t>N=1 n=303; 3.5% vs. 11.8%, OR=0.27, 95%CI: 0.1, 0.71</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -4869,7 +4869,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>TAAR1 agonists vs. placebo (addon) in any eligible population</t>
+          <t>TAAR1 agonists vs. antipsychotics in any eligible population</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -4879,17 +4879,17 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Nausea/vomitting</t>
+          <t>Worsening or exacerbation of schizophrenia</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>12 weeks</t>
+          <t>4 weeks</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>N=1 n=104; 3% vs. 5.4%, OR=0.54, 95%CI: 0.07, 3.99</t>
+          <t>N=1 n=214; 1.4% vs. 1.4%, OR=1.06, 95%CI: 0.09, 11.86</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -4899,7 +4899,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>1 eligible study with usable data.</t>
+          <t>50% of eligible studies and 91.8% of participants had usable data.</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -4916,7 +4916,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>TAAR1 agonists vs. placebo (addon) in any eligible population</t>
+          <t>TAAR1 agonists vs. antipsychotics in any eligible population</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -4926,17 +4926,17 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Sedation</t>
+          <t>Worsening or exacerbation of schizophrenia</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>12 weeks</t>
+          <t>52 weeks</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>N=1 n=104; 3% vs. 5.4%, OR=0.54, 95%CI: 0.07, 3.99</t>
+          <t>N=1 n=303; 10.5% vs. 5.9%, OR=1.87, 95%CI: 0.73, 4.78</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -4963,17 +4963,17 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>TAAR1 agonists vs. placebo (addon) in any eligible population</t>
+          <t>TAAR1 agonists vs. placebo (addon) in adults with schizophrenia and predominant negative symptoms</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>efficacy</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Insomnia</t>
+          <t>Overall symptoms</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -4983,7 +4983,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>N=1 n=104; not estimable effect size 0 events in both arms</t>
+          <t>N=1 n=76; SMD=0.26, 95%CI: -0.2, 0.72</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -5010,17 +5010,17 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>TAAR1 agonists vs. placebo (addon) in any eligible population</t>
+          <t>TAAR1 agonists vs. placebo (addon) in adults with schizophrenia and predominant negative symptoms</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>efficacy</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Headache</t>
+          <t>Response to treatment</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -5030,7 +5030,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>N=1 n=104; 1.5% vs. 8.1%, OR=0.17, 95%CI: 0.02, 1.71</t>
+          <t>N=1 n=104; 10.4% vs. 10.8%, OR=0.96, 95%CI: 0.26, 3.53</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -5057,17 +5057,17 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>TAAR1 agonists vs. placebo (addon) in any eligible population</t>
+          <t>TAAR1 agonists vs. placebo (addon) in adults with schizophrenia and predominant negative symptoms</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>efficacy</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Dizziness</t>
+          <t>Relapse</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -5077,7 +5077,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>N=1 n=104; 6% vs. 2.7%, OR=2.29, 95%CI: 0.25, 21.24</t>
+          <t>N=1 n=104; not estimable effect size 0 events in both arms</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -5104,45 +5104,656 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
+          <t>TAAR1 agonists vs. placebo (addon) in adults with schizophrenia and predominant negative symptoms</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>efficacy</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Positive symptoms</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>12 weeks</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>N=1 n=76; SMD=0.18, 95%CI: -0.28, 0.64</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>1 study with an overall low risk of bias.</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>1 eligible study with usable data.</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>No clear indication of indirectness.</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>No clear indication of other biases</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>TAAR1 agonists vs. placebo (addon) in adults with schizophrenia and predominant negative symptoms</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>efficacy</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Negative symptoms</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>12 weeks</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>N=1 n=75; SMD=0.25, 95%CI: -0.22, 0.71</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>1 study with an overall low risk of bias.</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>1 eligible study with usable data.</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>No clear indication of indirectness.</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>No clear indication of other biases</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
           <t>TAAR1 agonists vs. placebo (addon) in any eligible population</t>
         </is>
       </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr">
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Dropouts due to any reason</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>12 weeks</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>N=1 n=104; 8.9% vs. 10.8%, OR=0.81, 95%CI: 0.21, 3.08</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>1 study with an overall low risk of bias.</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>1 eligible study with usable data.</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>No clear indication of indirectness.</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>No clear indication of other biases</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>TAAR1 agonists vs. placebo (addon) in any eligible population</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Dropouts due to adverse events</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>12 weeks</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>N=1 n=104; 2.2% vs. 1.3%, OR=1.69, 95%CI: 0.07, 42.58</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>1 study with an overall low risk of bias.</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>1 eligible study with usable data.</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>No clear indication of indirectness.</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>No clear indication of other biases</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>TAAR1 agonists vs. placebo (addon) in any eligible population</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Any adverse event</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>12 weeks</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>N=1 n=104; 20.9% vs. 24.3%, OR=0.82, 95%CI: 0.32, 2.13</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>1 study with an overall low risk of bias.</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>1 eligible study with usable data.</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>No clear indication of indirectness.</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>No clear indication of other biases</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>TAAR1 agonists vs. placebo (addon) in any eligible population</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Serious adverse events</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>12 weeks</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>N=1 n=104; 3% vs. 2.7%, OR=1.11, 95%CI: 0.1, 12.64</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>1 study with an overall low risk of bias.</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>1 eligible study with usable data.</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>No clear indication of indirectness.</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>No clear indication of other biases</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>TAAR1 agonists vs. placebo (addon) in any eligible population</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Mortality due to any cause</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>12 weeks</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>N=1 n=104; 0.5% vs. 2.7%, OR=0.18, 95%CI: 0.01, 4.54</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>1 study with an overall low risk of bias.</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>1 eligible study with usable data.</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>No clear indication of indirectness.</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>No clear indication of other biases</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>TAAR1 agonists vs. placebo (addon) in any eligible population</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Nausea/vomitting</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>12 weeks</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>N=1 n=104; 3% vs. 5.4%, OR=0.54, 95%CI: 0.07, 3.99</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>1 study with an overall low risk of bias.</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>1 eligible study with usable data.</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>No clear indication of indirectness.</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>No clear indication of other biases</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>TAAR1 agonists vs. placebo (addon) in any eligible population</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Sedation</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>12 weeks</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>N=1 n=104; 3% vs. 5.4%, OR=0.54, 95%CI: 0.07, 3.99</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>1 study with an overall low risk of bias.</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>1 eligible study with usable data.</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>No clear indication of indirectness.</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>No clear indication of other biases</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>TAAR1 agonists vs. placebo (addon) in any eligible population</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Insomnia</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>12 weeks</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>N=1 n=104; not estimable effect size 0 events in both arms</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>1 study with an overall low risk of bias.</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>1 eligible study with usable data.</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>No clear indication of indirectness.</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>No clear indication of other biases</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>TAAR1 agonists vs. placebo (addon) in any eligible population</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Headache</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>12 weeks</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>N=1 n=104; 1.5% vs. 8.1%, OR=0.17, 95%CI: 0.02, 1.71</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>1 study with an overall low risk of bias.</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>1 eligible study with usable data.</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>No clear indication of indirectness.</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>No clear indication of other biases</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>TAAR1 agonists vs. placebo (addon) in any eligible population</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Dizziness</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>12 weeks</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>N=1 n=104; 6% vs. 2.7%, OR=2.29, 95%CI: 0.25, 21.24</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>1 study with an overall low risk of bias.</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>1 eligible study with usable data.</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>No clear indication of indirectness.</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>No clear indication of other biases</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>TAAR1 agonists vs. placebo (addon) in any eligible population</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
         <is>
           <t>Anticholinergic symptom</t>
         </is>
       </c>
-      <c r="D102" t="inlineStr">
+      <c r="D114" t="inlineStr">
         <is>
           <t>12 weeks</t>
         </is>
       </c>
-      <c r="E102" t="inlineStr">
+      <c r="E114" t="inlineStr">
         <is>
           <t>N=1 n=104; 2.2% vs. 1.3%, OR=1.69, 95%CI: 0.07, 42.58</t>
         </is>
       </c>
-      <c r="F102" t="inlineStr">
-        <is>
-          <t>1 study with an overall low risk of bias.</t>
-        </is>
-      </c>
-      <c r="G102" t="inlineStr">
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>1 study with an overall low risk of bias.</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
         <is>
           <t>1 eligible study with usable data.</t>
         </is>
       </c>
-      <c r="H102" t="inlineStr">
-        <is>
-          <t>No clear indication of indirectness.</t>
-        </is>
-      </c>
-      <c r="I102" t="inlineStr">
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>No clear indication of indirectness.</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>No clear indication of other biases</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>TAAR1 agonists vs. placebo (addon) in any eligible population</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Worsening or exacerbation of schizophrenia</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>12 weeks</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>N=1 n=104; not estimable effect size 0 events in both arms</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>1 study with an overall low risk of bias.</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>1 eligible study with usable data.</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>No clear indication of indirectness.</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
         <is>
           <t>No clear indication of other biases</t>
         </is>

--- a/data_u1/meta_outcome_soe.xlsx
+++ b/data_u1/meta_outcome_soe.xlsx
@@ -471,7 +471,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>N=4 n=1357; Random-effects: 23.7% vs. 18.7%, OR=1.35, 95%CI: 0.86, 2.12; Fixed-effecs: OR=1.39, 95%CI: 1.04, 1.86</t>
+          <t>N=4 n=1357; 24.4% vs. 18.7%, OR=1.4, 95%CI: 0.76, 2.58</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -518,7 +518,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>N=4 n=1291; Random-effects: SMD=0.13, 95%CI: 0, 0.26; Fixed-effecs: SMD=0.12, 95%CI: 0.01, 0.24</t>
+          <t>N=4 n=1291; Random-effects: SMD=0.12, 95%CI: -0.01, 0.24; Fixed-effecs: SMD=0.12, 95%CI: 0, 0.23</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -565,7 +565,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>N=4 n=1291; Random-effects: SMD=0.15, 95%CI: -0.02, 0.33; Fixed-effecs: SMD=0.14, 95%CI: 0.03, 0.26</t>
+          <t>N=4 n=1291; Random-effects: SMD=0.15, 95%CI: -0.02, 0.32; Fixed-effecs: SMD=0.14, 95%CI: 0.02, 0.25</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>1 study with an overall low risk of bias.</t>
+          <t>1 study with overall high risk of bias.</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -706,12 +706,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>N=1 n=27; 2.7% vs. 6.7%, OR=0.39, 95%CI: 0.01, 10.37</t>
+          <t>N=1 n=27; 2.7% vs. 6.7%, OR=0.39, 95%CI: 0.01, 11.78</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>1 study with an overall low risk of bias.</t>
+          <t>1 study with overall high risk of bias.</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>N=1 n=27; 2.7% vs. 6.7%, OR=0.39, 95%CI: 0.01, 10.37</t>
+          <t>N=1 n=27; 2.7% vs. 6.7%, OR=0.39, 95%CI: 0.01, 11.78</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -805,7 +805,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>1 study with an overall low risk of bias.</t>
+          <t>1 study with overall high risk of bias.</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -852,7 +852,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>1 study with an overall low risk of bias.</t>
+          <t>1 study with overall high risk of bias.</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -941,7 +941,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>N=1 n=39; 24% vs. 21.4%, OR=1.16, 95%CI: 0.24, 5.58</t>
+          <t>N=1 n=39; 23.1% vs. 21.4%, OR=1.1, 95%CI: 0.24, 5.08</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1129,7 +1129,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>N=7 n=1451; Random-effects: 23.4% vs. 19.9%, OR=1.23, 95%CI: 0.94, 1.61; Fixed-effecs: OR=1.24, 95%CI: 0.95, 1.62</t>
+          <t>N=7 n=1451; 23.5% vs. 19.9%, OR=1.24, 95%CI: 0.95, 1.62</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>N=7 n=1451; Random-effects: 9.8% vs. 6.4%, OR=1.57, 95%CI: 1.02, 2.42; Fixed-effecs: OR=1.62, 95%CI: 1.06, 2.47</t>
+          <t>N=7 n=1451; 9.9% vs. 6.4%, OR=1.6, 95%CI: 1.06, 2.42</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1317,7 +1317,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>N=7 n=1451; Random-effects: 42% vs. 38.9%, OR=1.14, 95%CI: 0.8, 1.63; Fixed-effecs: OR=1.21, 95%CI: 0.96, 1.52</t>
+          <t>N=7 n=1451; 43.5% vs. 38.9%, OR=1.21, 95%CI: 0.78, 1.86</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1411,7 +1411,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>N=7 n=1451; Random-effects: 5.8% vs. 4.5%, OR=1.31, 95%CI: 0.74, 2.32; Fixed-effecs: OR=1.35, 95%CI: 0.82, 2.24</t>
+          <t>N=7 n=1451; 5.9% vs. 4.5%, OR=1.33, 95%CI: 0.82, 2.18</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1505,7 +1505,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>N=7 n=1451; 3.2% vs. 1%, OR=3.15, 95%CI: 0.13, 78.11</t>
+          <t>N=7 n=1451; 2.8% vs. 1%, OR=2.71, 95%CI: 0.31, 23.65</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1599,7 +1599,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>N=6 n=987; Random-effects: 6.3% vs. 5.7%, OR=1.1, 95%CI: 0.62, 1.95; Fixed-effecs: OR=1.16, 95%CI: 0.66, 2.02</t>
+          <t>N=7 n=1451; 5.8% vs. 4.5%, OR=1.31, 95%CI: 0.75, 2.29</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1609,12 +1609,12 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>75% of eligible studies and 63.1% of participants had usable data.</t>
+          <t>87.5% of eligible studies and 92.7% of participants had usable data.</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>66.7% studies and 93.2% participants with schizophrenia.</t>
+          <t>71.4% studies and 95.4% participants with schizophrenia.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -1693,7 +1693,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>N=2 n=458; Random-effects: 1.1% vs. 1%, OR=1.04, 95%CI: 0.17, 6.47; Fixed-effecs: OR=1.04, 95%CI: 0.17, 6.47</t>
+          <t>N=2 n=458; 1% vs. 1%, OR=0.98, 95%CI: 0.2, 4.83</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1787,7 +1787,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>N=1 n=24; not estimable effect size 0 events in both arms</t>
+          <t>N=1 n=24; 2% vs. 2%, OR=1, 95%CI: 0.02, 56.91</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1834,7 +1834,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>N=3 n=1144; Random-effects: 2.9% vs. 2.8%, OR=1.02, 95%CI: 0.49, 2.12; Fixed-effecs: OR=1.02, 95%CI: 0.49, 2.12</t>
+          <t>N=3 n=1144; 2.8% vs. 2.8%, OR=1, 95%CI: 0.49, 2.04</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1881,7 +1881,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>N=1 n=245; 1.2% vs. 0.4%, OR=3.15, 95%CI: 0.13, 78.11</t>
+          <t>N=1 n=245; 1.2% vs. 0.4%, OR=3.15, 95%CI: 0.13, 79.12</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1928,7 +1928,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>N=5 n=1385; Random-effects: 5.5% vs. 4.7%, OR=1.19, 95%CI: 0.71, 1.99; Fixed-effecs: OR=1.22, 95%CI: 0.73, 2.04</t>
+          <t>N=5 n=1385; 5.6% vs. 4.7%, OR=1.21, 95%CI: 0.73, 2</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1975,7 +1975,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>N=1 n=69; not estimable effect size 0 events in both arms</t>
+          <t>N=1 n=69; 1.4% vs. 1.4%, OR=0.97, 95%CI: 0.02, 53.31</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -2022,7 +2022,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>N=5 n=1385; Random-effects: 5.2% vs. 5.8%, OR=0.89, 95%CI: 0.3, 2.64; Fixed-effecs: OR=1.17, 95%CI: 0.73, 1.89</t>
+          <t>N=5 n=1385; 6.7% vs. 5.8%, OR=1.16, 95%CI: 0.58, 2.34</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -2116,7 +2116,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>N=5 n=774; Random-effects: 5.5% vs. 4.7%, OR=1.18, 95%CI: 0.47, 2.99; Fixed-effecs: OR=1.24, 95%CI: 0.48, 3.18</t>
+          <t>N=5 n=774; 5.7% vs. 4.7%, OR=1.22, 95%CI: 0.5, 2.98</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -2163,7 +2163,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>N=7 n=1451; Random-effects: 8.5% vs. 7.4%, OR=1.16, 95%CI: 0.57, 2.34; Fixed-effecs: OR=1.15, 95%CI: 0.75, 1.76</t>
+          <t>N=7 n=1451; 8.3% vs. 7.4%, OR=1.14, 95%CI: 0.75, 1.72</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -2210,7 +2210,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>N=1 n=69; 11.5% vs. 20.6%, OR=0.5, 95%CI: 0.13, 1.89</t>
+          <t>N=1 n=69; 11.9% vs. 20.6%, OR=0.52, 95%CI: 0.14, 1.91</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -2257,7 +2257,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>N=6 n=1412; Random-effects: 10.7% vs. 8.5%, OR=1.29, 95%CI: 0.86, 1.95; Fixed-effecs: OR=1.32, 95%CI: 0.89, 1.94</t>
+          <t>N=6 n=1412; 10.8% vs. 8.5%, OR=1.3, 95%CI: 0.89, 1.9</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>N=2 n=92; 8.1% vs. 1.6%, OR=5.32, 95%CI: 0.6, 46.78</t>
+          <t>N=2 n=92; 6% vs. 1.6%, OR=3.88, 95%CI: 0.65, 23.17</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -2398,7 +2398,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>N=1 n=245; not estimable effect size 0 events in both arms</t>
+          <t>N=1 n=245; 0.4% vs. 0.4%, OR=1.04, 95%CI: 0.02, 53.77</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -2445,7 +2445,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>N=1 n=39; 52.4% vs. 78.6%, OR=0.3, 95%CI: 0.07, 1.32</t>
+          <t>N=1 n=39; 54.8% vs. 78.6%, OR=0.33, 95%CI: 0.08, 1.42</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2539,7 +2539,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>N=4 n=529; Random-effects: 6.2% vs. 2.9%, OR=2.23, 95%CI: 0.34, 14.68; Fixed-effecs: OR=3.14, 95%CI: 0.33, 29.62</t>
+          <t>N=4 n=529; 6.4% vs. 2.9%, OR=2.28, 95%CI: 0.4, 12.9</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>N=1 n=69; 15.3% vs. 1.4%, OR=12.44, 95%CI: 0.66, 234.38</t>
+          <t>N=1 n=69; 15.3% vs. 1.4%, OR=12.44, 95%CI: 0.63, 244.61</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2633,7 +2633,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>N=3 n=490; Random-effects: 3.3% vs. 2.6%, OR=1.28, 95%CI: 0.15, 11.23; Fixed-effecs: OR=1.44, 95%CI: 0.14, 15.03</t>
+          <t>N=3 n=490; 3.3% vs. 2.6%, OR=1.27, 95%CI: 0.18, 9.01</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2680,7 +2680,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>N=6 n=1412; Random-effects: 6.5% vs. 4.4%, OR=1.49, 95%CI: 0.73, 3.08; Fixed-effecs: OR=1.78, 95%CI: 1.07, 2.95</t>
+          <t>N=6 n=1412; 7.4% vs. 4.4%, OR=1.73, 95%CI: 0.99, 3.02</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2774,7 +2774,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>N=1 n=214; 7.9% vs. 13.5%, OR=0.55, 95%CI: 0.22, 1.35</t>
+          <t>N=1 n=214; 7.9% vs. 13.5%, OR=0.55, 95%CI: 0.22, 1.33</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -3009,7 +3009,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>N=1 n=303; 3% vs. 2%, OR=1.54, 95%CI: 0.3, 7.76</t>
+          <t>N=1 n=303; 2.6% vs. 2%, OR=1.34, 95%CI: 0.3, 5.9</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -3056,7 +3056,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>N=1 n=71; 14.3% vs. 5.6%, OR=2.83, 95%CI: 0.51, 15.69</t>
+          <t>N=1 n=71; 12.8% vs. 5.6%, OR=2.49, 95%CI: 0.51, 12.26</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -3103,7 +3103,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>N=1 n=214; 22.9% vs. 18.9%, OR=1.27, 95%CI: 0.63, 2.56</t>
+          <t>N=1 n=214; 22.6% vs. 18.9%, OR=1.25, 95%CI: 0.62, 2.51</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -3197,7 +3197,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>N=1 n=71; not estimable effect size 0 events in both arms</t>
+          <t>N=1 n=71; 1.4% vs. 1.4%, OR=1.03, 95%CI: 0.02, 56.27</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -3244,7 +3244,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>N=1 n=214; 6.4% vs. 1.4%, OR=5.02, 95%CI: 0.62, 40.38</t>
+          <t>N=1 n=214; 4.6% vs. 1.4%, OR=3.54, 95%CI: 0.61, 20.5</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -3291,7 +3291,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>N=1 n=303; 23.9% vs. 20.6%, OR=1.21, 95%CI: 0.68, 2.16</t>
+          <t>N=1 n=303; 23.7% vs. 20.6%, OR=1.2, 95%CI: 0.67, 2.13</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -3338,7 +3338,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>N=2 n=133; Random-effects: 87.2% vs. 36%, OR=12.17, 95%CI: 1.22, 121.04; Fixed-effecs: OR=9.49, 95%CI: 3.94, 22.84</t>
+          <t>N=2 n=133; 83.6% vs. 36%, OR=9.09, 95%CI: 0.15, 551.27</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -3385,7 +3385,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>N=1 n=214; 26.5% vs. 48.6%, OR=0.38, 95%CI: 0.21, 0.68</t>
+          <t>N=1 n=214; 26.5% vs. 48.6%, OR=0.38, 95%CI: 0.21, 0.69</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -3432,7 +3432,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>N=1 n=303; 76% vs. 75.5%, OR=1.03, 95%CI: 0.59, 1.8</t>
+          <t>N=1 n=303; 76.2% vs. 75.5%, OR=1.04, 95%CI: 0.6, 1.81</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>N=2 n=133; 4.5% vs. 1.5%, OR=3.17, 95%CI: 0.13, 80.58</t>
+          <t>N=2 n=133; 4.4% vs. 1.5%, OR=3.12, 95%CI: 0.17, 57.75</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -3526,7 +3526,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>N=1 n=214; 2.5% vs. 0.7%, OR=3.79, 95%CI: 0.19, 74.42</t>
+          <t>N=1 n=214; 2.5% vs. 0.7%, OR=3.79, 95%CI: 0.19, 75.83</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -3573,7 +3573,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>N=1 n=303; 8.2% vs. 0.5%, OR=18.23, 95%CI: 1.08, 307.1</t>
+          <t>N=1 n=303; 8.2% vs. 0.5%, OR=18.23, 95%CI: 1.07, 311.31</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -3620,7 +3620,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>N=2 n=133; not estimable effect size 0 events in both arms</t>
+          <t>N=2 n=133; 1.5% vs. 1.5%, OR=1.01, 95%CI: 0.04, 26.28</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -3667,7 +3667,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>N=1 n=214; not estimable effect size 0 events in both arms</t>
+          <t>N=1 n=214; 0.4% vs. 0.7%, OR=0.53, 95%CI: 0.01, 27.55</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -3714,7 +3714,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>N=1 n=303; not estimable effect size 0 events in both arms</t>
+          <t>N=1 n=303; 0.2% vs. 0.5%, OR=0.51, 95%CI: 0.01, 26.2</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -3761,7 +3761,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>N=2 n=133; Random-effects: 30.5% vs. 1.5%, OR=29.82, 95%CI: 3.87, 229.8; Fixed-effecs: OR=Inf, 95%CI: NaN, NaN</t>
+          <t>N=2 n=133; 46.6% vs. 1.5%, OR=59.21, 95%CI: 3.57, 982.99</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -3808,7 +3808,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>N=1 n=214; 1.4% vs. 8.1%, OR=0.16, 95%CI: 0.03, 0.84</t>
+          <t>N=1 n=214; 1.6% vs. 8.1%, OR=0.19, 95%CI: 0.04, 0.85</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3855,7 +3855,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>N=1 n=303; 6.5% vs. 3.9%, OR=1.69, 95%CI: 0.54, 5.33</t>
+          <t>N=1 n=303; 6% vs. 3.9%, OR=1.57, 95%CI: 0.52, 4.7</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3949,7 +3949,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>N=1 n=214; 1.4% vs. 10.8%, OR=0.12, 95%CI: 0.02, 0.58</t>
+          <t>N=1 n=214; 1.7% vs. 10.8%, OR=0.14, 95%CI: 0.03, 0.6</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3996,7 +3996,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>N=1 n=303; 4.5% vs. 10.8%, OR=0.39, 95%CI: 0.16, 0.97</t>
+          <t>N=1 n=303; 4.5% vs. 10.8%, OR=0.39, 95%CI: 0.16, 0.96</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -4090,7 +4090,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>N=1 n=303; 7% vs. 2%, OR=3.74, 95%CI: 0.83, 16.8</t>
+          <t>N=1 n=303; 5.9% vs. 2%, OR=3.11, 95%CI: 0.79, 12.24</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -4137,7 +4137,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>N=1 n=214; 6% vs. 0.7%, OR=9.56, 95%CI: 0.54, 167.96</t>
+          <t>N=1 n=214; 6% vs. 0.7%, OR=9.56, 95%CI: 0.53, 171.14</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -4184,7 +4184,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>N=1 n=71; 1.2% vs. 8.3%, OR=0.13, 95%CI: 0.01, 2.71</t>
+          <t>N=1 n=71; 1.2% vs. 8.3%, OR=0.13, 95%CI: 0.01, 2.83</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -4231,7 +4231,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>N=1 n=214; 3.6% vs. 6.8%, OR=0.51, 95%CI: 0.14, 1.83</t>
+          <t>N=1 n=214; 3.6% vs. 6.8%, OR=0.51, 95%CI: 0.15, 1.74</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -4278,7 +4278,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>N=1 n=303; 13.5% vs. 9.8%, OR=1.43, 95%CI: 0.66, 3.08</t>
+          <t>N=1 n=303; 13.1% vs. 9.8%, OR=1.39, 95%CI: 0.65, 2.96</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -4325,7 +4325,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>N=2 n=133; Random-effects: 42.9% vs. 8.6%, OR=7.96, 95%CI: 2.84, 22.36; Fixed-effecs: OR=7.81, 95%CI: 2.76, 22.09</t>
+          <t>N=2 n=133; 41.5% vs. 8.6%, OR=7.49, 95%CI: 2.69, 20.84</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -4372,7 +4372,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>N=1 n=303; 5.9% vs. 20.6%, OR=0.24, 95%CI: 0.12, 0.52</t>
+          <t>N=1 n=303; 6.1% vs. 20.6%, OR=0.25, 95%CI: 0.12, 0.53</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -4419,7 +4419,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>N=1 n=214; 5.7% vs. 6.8%, OR=0.84, 95%CI: 0.26, 2.65</t>
+          <t>N=1 n=214; 5.5% vs. 6.8%, OR=0.81, 95%CI: 0.27, 2.48</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -4466,7 +4466,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>N=1 n=303; 14.9% vs. 10.8%, OR=1.45, 95%CI: 0.7, 3.03</t>
+          <t>N=1 n=303; 14.7% vs. 10.8%, OR=1.42, 95%CI: 0.68, 2.93</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -4513,7 +4513,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>N=1 n=71; 11.4% vs. 2.8%, OR=4.52, 95%CI: 0.48, 42.59</t>
+          <t>N=1 n=71; 8.8% vs. 2.8%, OR=3.38, 95%CI: 0.49, 23.43</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -4560,7 +4560,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>N=1 n=214; 6.4% vs. 8.1%, OR=0.78, 95%CI: 0.27, 2.28</t>
+          <t>N=1 n=214; 6.3% vs. 8.1%, OR=0.76, 95%CI: 0.27, 2.17</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -4607,7 +4607,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>N=1 n=303; 10% vs. 7.8%, OR=1.3, 95%CI: 0.55, 3.06</t>
+          <t>N=1 n=303; 9.7% vs. 7.8%, OR=1.26, 95%CI: 0.54, 2.91</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -4654,7 +4654,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>N=1 n=62; not estimable effect size 0 events in both arms</t>
+          <t>N=1 n=62; 1.6% vs. 1.6%, OR=1, 95%CI: 0.02, 55.38</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -4701,7 +4701,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>N=2 n=133; Random-effects: 22.8% vs. 2.3%, OR=12.62, 95%CI: 2.25, 70.79; Fixed-effecs: OR=19.68, 95%CI: 2.39, 162.25</t>
+          <t>N=2 n=133; 23.1% vs. 2.3%, OR=12.78, 95%CI: 2.29, 71.32</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -4748,7 +4748,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>N=1 n=303; 8% vs. 4.9%, OR=1.68, 95%CI: 0.6, 4.72</t>
+          <t>N=1 n=303; 7.5% vs. 4.9%, OR=1.58, 95%CI: 0.58, 4.29</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -4795,7 +4795,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>N=1 n=71; 15.3% vs. 1.4%, OR=13.16, 95%CI: 0.7, 247.71</t>
+          <t>N=1 n=71; 15.3% vs. 1.4%, OR=13.16, 95%CI: 0.67, 257.97</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -4842,7 +4842,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>N=1 n=303; 3.5% vs. 11.8%, OR=0.27, 95%CI: 0.1, 0.71</t>
+          <t>N=1 n=303; 3.6% vs. 11.8%, OR=0.28, 95%CI: 0.11, 0.72</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -4889,7 +4889,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>N=1 n=214; 1.4% vs. 1.4%, OR=1.06, 95%CI: 0.09, 11.86</t>
+          <t>N=1 n=214; 1.2% vs. 1.4%, OR=0.88, 95%CI: 0.11, 6.91</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -4936,7 +4936,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>N=1 n=303; 10.5% vs. 5.9%, OR=1.87, 95%CI: 0.73, 4.78</t>
+          <t>N=1 n=303; 10% vs. 5.9%, OR=1.77, 95%CI: 0.71, 4.42</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -5030,7 +5030,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>N=1 n=104; 10.4% vs. 10.8%, OR=0.96, 95%CI: 0.26, 3.53</t>
+          <t>N=1 n=104; 10% vs. 10.8%, OR=0.92, 95%CI: 0.26, 3.24</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -5077,7 +5077,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>N=1 n=104; not estimable effect size 0 events in both arms</t>
+          <t>N=1 n=104; 0.7% vs. 1.3%, OR=0.56, 95%CI: 0.01, 29.77</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -5218,7 +5218,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>N=1 n=104; 8.9% vs. 10.8%, OR=0.81, 95%CI: 0.21, 3.08</t>
+          <t>N=1 n=104; 8.7% vs. 10.8%, OR=0.79, 95%CI: 0.22, 2.85</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -5265,7 +5265,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>N=1 n=104; 2.2% vs. 1.3%, OR=1.69, 95%CI: 0.07, 42.58</t>
+          <t>N=1 n=104; 2.2% vs. 1.3%, OR=1.69, 95%CI: 0.06, 44.25</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -5312,7 +5312,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>N=1 n=104; 20.9% vs. 24.3%, OR=0.82, 95%CI: 0.32, 2.13</t>
+          <t>N=1 n=104; 20.7% vs. 24.3%, OR=0.81, 95%CI: 0.32, 2.09</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -5359,7 +5359,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>N=1 n=104; 3% vs. 2.7%, OR=1.11, 95%CI: 0.1, 12.64</t>
+          <t>N=1 n=104; 2.5% vs. 2.7%, OR=0.93, 95%CI: 0.12, 7.49</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -5406,7 +5406,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>N=1 n=104; 0.5% vs. 2.7%, OR=0.18, 95%CI: 0.01, 4.54</t>
+          <t>N=1 n=104; 0.5% vs. 2.7%, OR=0.18, 95%CI: 0.01, 4.67</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -5453,7 +5453,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>N=1 n=104; 3% vs. 5.4%, OR=0.54, 95%CI: 0.07, 3.99</t>
+          <t>N=1 n=104; 3% vs. 5.4%, OR=0.54, 95%CI: 0.09, 3.34</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -5500,7 +5500,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>N=1 n=104; 3% vs. 5.4%, OR=0.54, 95%CI: 0.07, 3.99</t>
+          <t>N=1 n=104; 3% vs. 5.4%, OR=0.54, 95%CI: 0.09, 3.34</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -5547,7 +5547,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>N=1 n=104; not estimable effect size 0 events in both arms</t>
+          <t>N=1 n=104; 0.7% vs. 1.3%, OR=0.56, 95%CI: 0.01, 29.77</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -5594,7 +5594,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>N=1 n=104; 1.5% vs. 8.1%, OR=0.17, 95%CI: 0.02, 1.71</t>
+          <t>N=1 n=104; 1.9% vs. 8.1%, OR=0.22, 95%CI: 0.03, 1.6</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -5641,7 +5641,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>N=1 n=104; 6% vs. 2.7%, OR=2.29, 95%CI: 0.25, 21.24</t>
+          <t>N=1 n=104; 4.6% vs. 2.7%, OR=1.72, 95%CI: 0.25, 11.7</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -5688,7 +5688,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>N=1 n=104; 2.2% vs. 1.3%, OR=1.69, 95%CI: 0.07, 42.58</t>
+          <t>N=1 n=104; 2.2% vs. 1.3%, OR=1.69, 95%CI: 0.06, 44.25</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -5735,7 +5735,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>N=1 n=104; not estimable effect size 0 events in both arms</t>
+          <t>N=1 n=104; 0.7% vs. 1.3%, OR=0.56, 95%CI: 0.01, 29.77</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">

--- a/data_u1/meta_outcome_soe.xlsx
+++ b/data_u1/meta_outcome_soe.xlsx
@@ -471,7 +471,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>N=4 n=1357; 24.4% vs. 18.7%, OR=1.4, 95%CI: 0.76, 2.58</t>
+          <t>N=4 n=1357; Random-effects: 23.7% vs. 18.7%, OR=1.35, 95%CI: 0.86, 2.12; Fixed-effecs: OR=1.39, 95%CI: 1.04, 1.86</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -706,7 +706,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>N=1 n=27; 2.7% vs. 6.7%, OR=0.39, 95%CI: 0.01, 11.78</t>
+          <t>N=1 n=27; 2.7% vs. 6.7%, OR=0.39, 95%CI: 0.01, 10.37</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>N=1 n=27; 2.7% vs. 6.7%, OR=0.39, 95%CI: 0.01, 11.78</t>
+          <t>N=1 n=27; 2.7% vs. 6.7%, OR=0.39, 95%CI: 0.01, 10.37</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -941,7 +941,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>N=1 n=39; 23.1% vs. 21.4%, OR=1.1, 95%CI: 0.24, 5.08</t>
+          <t>N=1 n=39; 24% vs. 21.4%, OR=1.16, 95%CI: 0.24, 5.58</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1129,7 +1129,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>N=7 n=1451; 23.5% vs. 19.9%, OR=1.24, 95%CI: 0.95, 1.62</t>
+          <t>N=7 n=1451; Random-effects: 23.4% vs. 19.9%, OR=1.23, 95%CI: 0.94, 1.61; Fixed-effecs: OR=1.24, 95%CI: 0.95, 1.62</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>N=7 n=1451; 9.9% vs. 6.4%, OR=1.6, 95%CI: 1.06, 2.42</t>
+          <t>N=7 n=1451; Random-effects: 9.8% vs. 6.4%, OR=1.57, 95%CI: 1.02, 2.42; Fixed-effecs: OR=1.62, 95%CI: 1.06, 2.47</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1317,7 +1317,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>N=7 n=1451; 43.5% vs. 38.9%, OR=1.21, 95%CI: 0.78, 1.86</t>
+          <t>N=7 n=1451; Random-effects: 42% vs. 38.9%, OR=1.14, 95%CI: 0.8, 1.63; Fixed-effecs: OR=1.21, 95%CI: 0.96, 1.52</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1411,7 +1411,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>N=7 n=1451; 5.9% vs. 4.5%, OR=1.33, 95%CI: 0.82, 2.18</t>
+          <t>N=7 n=1451; Random-effects: 5.8% vs. 4.5%, OR=1.31, 95%CI: 0.74, 2.32; Fixed-effecs: OR=1.34, 95%CI: 0.81, 2.2</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1505,7 +1505,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>N=7 n=1451; 2.8% vs. 1%, OR=2.71, 95%CI: 0.31, 23.65</t>
+          <t>N=7 n=1451; 3.2% vs. 1%, OR=3.15, 95%CI: 0.13, 78.11</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1599,7 +1599,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>N=7 n=1451; 5.8% vs. 4.5%, OR=1.31, 95%CI: 0.75, 2.29</t>
+          <t>N=7 n=1451; Random-effects: 5.6% vs. 4.5%, OR=1.24, 95%CI: 0.73, 2.11; Fixed-effecs: OR=1.31, 95%CI: 0.79, 2.17</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1693,7 +1693,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>N=2 n=458; 1% vs. 1%, OR=0.98, 95%CI: 0.2, 4.83</t>
+          <t>N=2 n=458; Random-effects: 1.1% vs. 1%, OR=1.04, 95%CI: 0.17, 6.47; Fixed-effecs: OR=1.04, 95%CI: 0.17, 6.47</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1787,7 +1787,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>N=1 n=24; 2% vs. 2%, OR=1, 95%CI: 0.02, 56.91</t>
+          <t>N=1 n=24; not estimable effect size 0 events in both arms</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1834,7 +1834,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>N=3 n=1144; 2.8% vs. 2.8%, OR=1, 95%CI: 0.49, 2.04</t>
+          <t>N=3 n=1144; Random-effects: 2.9% vs. 2.8%, OR=1.02, 95%CI: 0.49, 2.12; Fixed-effecs: OR=1.02, 95%CI: 0.49, 2.12</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1881,7 +1881,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>N=1 n=245; 1.2% vs. 0.4%, OR=3.15, 95%CI: 0.13, 79.12</t>
+          <t>N=1 n=245; 1.2% vs. 0.4%, OR=3.15, 95%CI: 0.13, 78.11</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1928,7 +1928,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>N=5 n=1385; 5.6% vs. 4.7%, OR=1.21, 95%CI: 0.73, 2</t>
+          <t>N=5 n=1385; Random-effects: 5.5% vs. 4.7%, OR=1.19, 95%CI: 0.71, 1.99; Fixed-effecs: OR=1.21, 95%CI: 0.72, 2.01</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1975,7 +1975,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>N=1 n=69; 1.4% vs. 1.4%, OR=0.97, 95%CI: 0.02, 53.31</t>
+          <t>N=1 n=69; not estimable effect size 0 events in both arms</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -2022,7 +2022,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>N=5 n=1385; 6.7% vs. 5.8%, OR=1.16, 95%CI: 0.58, 2.34</t>
+          <t>N=5 n=1385; Random-effects: 5.2% vs. 5.8%, OR=0.89, 95%CI: 0.3, 2.64; Fixed-effecs: OR=1.17, 95%CI: 0.73, 1.89</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -2116,7 +2116,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>N=5 n=774; 5.7% vs. 4.7%, OR=1.22, 95%CI: 0.5, 2.98</t>
+          <t>N=5 n=774; Random-effects: 5.5% vs. 4.7%, OR=1.18, 95%CI: 0.47, 2.99; Fixed-effecs: OR=1.19, 95%CI: 0.48, 2.98</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -2163,7 +2163,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>N=7 n=1451; 8.3% vs. 7.4%, OR=1.14, 95%CI: 0.75, 1.72</t>
+          <t>N=7 n=1451; Random-effects: 8.5% vs. 7.4%, OR=1.16, 95%CI: 0.57, 2.34; Fixed-effecs: OR=1.15, 95%CI: 0.75, 1.76</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -2210,7 +2210,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>N=1 n=69; 11.9% vs. 20.6%, OR=0.52, 95%CI: 0.14, 1.91</t>
+          <t>N=1 n=69; 11.5% vs. 20.6%, OR=0.5, 95%CI: 0.13, 1.89</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -2257,7 +2257,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>N=6 n=1412; 10.8% vs. 8.5%, OR=1.3, 95%CI: 0.89, 1.9</t>
+          <t>N=6 n=1412; Random-effects: 10.7% vs. 8.5%, OR=1.29, 95%CI: 0.86, 1.95; Fixed-effecs: OR=1.32, 95%CI: 0.89, 1.94</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>N=2 n=92; 6% vs. 1.6%, OR=3.88, 95%CI: 0.65, 23.17</t>
+          <t>N=2 n=92; 8.1% vs. 1.6%, OR=5.32, 95%CI: 0.6, 46.78</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -2398,7 +2398,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>N=1 n=245; 0.4% vs. 0.4%, OR=1.04, 95%CI: 0.02, 53.77</t>
+          <t>N=1 n=245; not estimable effect size 0 events in both arms</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -2445,7 +2445,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>N=1 n=39; 54.8% vs. 78.6%, OR=0.33, 95%CI: 0.08, 1.42</t>
+          <t>N=1 n=39; 52.4% vs. 78.6%, OR=0.3, 95%CI: 0.07, 1.32</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2539,7 +2539,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>N=4 n=529; 6.4% vs. 2.9%, OR=2.28, 95%CI: 0.4, 12.9</t>
+          <t>N=4 n=529; Random-effects: 6.2% vs. 2.9%, OR=2.23, 95%CI: 0.34, 14.68; Fixed-effecs: OR=2.24, 95%CI: 0.34, 14.7</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>N=1 n=69; 15.3% vs. 1.4%, OR=12.44, 95%CI: 0.63, 244.61</t>
+          <t>N=1 n=69; 15.3% vs. 1.4%, OR=12.44, 95%CI: 0.66, 234.38</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2633,7 +2633,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>N=3 n=490; 3.3% vs. 2.6%, OR=1.27, 95%CI: 0.18, 9.01</t>
+          <t>N=3 n=490; Random-effects: 3.3% vs. 2.6%, OR=1.28, 95%CI: 0.15, 11.23; Fixed-effecs: OR=1.39, 95%CI: 0.18, 10.67</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2670,7 +2670,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Worsening or exacerbation of schizophrenia</t>
+          <t>Worsening or exacerbation of psychosis</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -2680,7 +2680,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>N=6 n=1412; 7.4% vs. 4.4%, OR=1.73, 95%CI: 0.99, 3.02</t>
+          <t>N=7 n=1451; Random-effects: 7.4% vs. 4.9%, OR=1.57, 95%CI: 0.86, 2.9; Fixed-effecs: OR=1.75, 95%CI: 1.09, 2.83</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2690,12 +2690,12 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>75% of eligible studies and 90.2% of participants had usable data.</t>
+          <t>87.5% of eligible studies and 92.7% of participants had usable data.</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>83.3% studies and 98% participants with schizophrenia.</t>
+          <t>71.4% studies and 95.4% participants with schizophrenia.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -2774,7 +2774,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>N=1 n=214; 7.9% vs. 13.5%, OR=0.55, 95%CI: 0.22, 1.33</t>
+          <t>N=1 n=214; 7.9% vs. 13.5%, OR=0.55, 95%CI: 0.22, 1.35</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -3009,7 +3009,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>N=1 n=303; 2.6% vs. 2%, OR=1.34, 95%CI: 0.3, 5.9</t>
+          <t>N=1 n=303; 5.2% vs. 0.5%, OR=11.24, 95%CI: 0.65, 193.78</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -3056,7 +3056,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>N=1 n=71; 12.8% vs. 5.6%, OR=2.49, 95%CI: 0.51, 12.26</t>
+          <t>N=1 n=71; 14.3% vs. 5.6%, OR=2.83, 95%CI: 0.51, 15.69</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -3103,7 +3103,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>N=1 n=214; 22.6% vs. 18.9%, OR=1.25, 95%CI: 0.62, 2.51</t>
+          <t>N=1 n=214; 22.9% vs. 18.9%, OR=1.27, 95%CI: 0.63, 2.56</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -3197,7 +3197,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>N=1 n=71; 1.4% vs. 1.4%, OR=1.03, 95%CI: 0.02, 56.27</t>
+          <t>N=1 n=71; not estimable effect size 0 events in both arms</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -3244,7 +3244,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>N=1 n=214; 4.6% vs. 1.4%, OR=3.54, 95%CI: 0.61, 20.5</t>
+          <t>N=1 n=214; 6.4% vs. 1.4%, OR=5.02, 95%CI: 0.62, 40.38</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -3291,7 +3291,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>N=1 n=303; 23.7% vs. 20.6%, OR=1.2, 95%CI: 0.67, 2.13</t>
+          <t>N=1 n=303; 23.9% vs. 20.6%, OR=1.21, 95%CI: 0.68, 2.16</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -3338,7 +3338,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>N=2 n=133; 83.6% vs. 36%, OR=9.09, 95%CI: 0.15, 551.27</t>
+          <t>N=2 n=133; Random-effects: 87.2% vs. 36%, OR=12.17, 95%CI: 1.22, 121.04; Fixed-effecs: OR=9.49, 95%CI: 3.94, 22.84</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -3385,7 +3385,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>N=1 n=214; 26.5% vs. 48.6%, OR=0.38, 95%CI: 0.21, 0.69</t>
+          <t>N=1 n=214; 26.5% vs. 48.6%, OR=0.38, 95%CI: 0.21, 0.68</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -3432,7 +3432,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>N=1 n=303; 76.2% vs. 75.5%, OR=1.04, 95%CI: 0.6, 1.81</t>
+          <t>N=1 n=303; 76% vs. 75.5%, OR=1.03, 95%CI: 0.59, 1.8</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>N=2 n=133; 4.4% vs. 1.5%, OR=3.12, 95%CI: 0.17, 57.75</t>
+          <t>N=2 n=133; 4.5% vs. 1.5%, OR=3.17, 95%CI: 0.13, 80.58</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -3526,7 +3526,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>N=1 n=214; 2.5% vs. 0.7%, OR=3.79, 95%CI: 0.19, 75.83</t>
+          <t>N=1 n=214; 2.5% vs. 0.7%, OR=3.79, 95%CI: 0.19, 74.42</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -3573,7 +3573,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>N=1 n=303; 8.2% vs. 0.5%, OR=18.23, 95%CI: 1.07, 311.31</t>
+          <t>N=1 n=303; 8.2% vs. 0.5%, OR=18.23, 95%CI: 1.08, 307.1</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -3620,7 +3620,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>N=2 n=133; 1.5% vs. 1.5%, OR=1.01, 95%CI: 0.04, 26.28</t>
+          <t>N=2 n=133; not estimable effect size 0 events in both arms</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -3667,7 +3667,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>N=1 n=214; 0.4% vs. 0.7%, OR=0.53, 95%CI: 0.01, 27.55</t>
+          <t>N=1 n=214; not estimable effect size 0 events in both arms</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -3714,7 +3714,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>N=1 n=303; 0.2% vs. 0.5%, OR=0.51, 95%CI: 0.01, 26.2</t>
+          <t>N=1 n=303; not estimable effect size 0 events in both arms</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -3761,7 +3761,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>N=2 n=133; 46.6% vs. 1.5%, OR=59.21, 95%CI: 3.57, 982.99</t>
+          <t>N=2 n=133; Random-effects: 30.5% vs. 1.5%, OR=29.82, 95%CI: 3.87, 229.8; Fixed-effecs: OR=30.28, 95%CI: 3.95, 231.96</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -3808,7 +3808,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>N=1 n=214; 1.6% vs. 8.1%, OR=0.19, 95%CI: 0.04, 0.85</t>
+          <t>N=1 n=214; 1.4% vs. 8.1%, OR=0.16, 95%CI: 0.03, 0.84</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3855,7 +3855,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>N=1 n=303; 6% vs. 3.9%, OR=1.57, 95%CI: 0.52, 4.7</t>
+          <t>N=1 n=303; 6.5% vs. 3.9%, OR=1.69, 95%CI: 0.54, 5.33</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3949,7 +3949,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>N=1 n=214; 1.7% vs. 10.8%, OR=0.14, 95%CI: 0.03, 0.6</t>
+          <t>N=1 n=214; 1.4% vs. 10.8%, OR=0.12, 95%CI: 0.02, 0.58</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3996,7 +3996,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>N=1 n=303; 4.5% vs. 10.8%, OR=0.39, 95%CI: 0.16, 0.96</t>
+          <t>N=1 n=303; 4.5% vs. 10.8%, OR=0.39, 95%CI: 0.16, 0.97</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -4090,7 +4090,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>N=1 n=303; 5.9% vs. 2%, OR=3.11, 95%CI: 0.79, 12.24</t>
+          <t>N=1 n=303; 7% vs. 2%, OR=3.74, 95%CI: 0.83, 16.8</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -4137,7 +4137,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>N=1 n=214; 6% vs. 0.7%, OR=9.56, 95%CI: 0.53, 171.14</t>
+          <t>N=1 n=214; 6% vs. 0.7%, OR=9.56, 95%CI: 0.54, 167.96</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -4184,7 +4184,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>N=1 n=71; 1.2% vs. 8.3%, OR=0.13, 95%CI: 0.01, 2.83</t>
+          <t>N=1 n=71; 1.2% vs. 8.3%, OR=0.13, 95%CI: 0.01, 2.71</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -4231,7 +4231,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>N=1 n=214; 3.6% vs. 6.8%, OR=0.51, 95%CI: 0.15, 1.74</t>
+          <t>N=1 n=214; 3.6% vs. 6.8%, OR=0.51, 95%CI: 0.14, 1.83</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -4278,7 +4278,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>N=1 n=303; 13.1% vs. 9.8%, OR=1.39, 95%CI: 0.65, 2.96</t>
+          <t>N=1 n=303; 13.5% vs. 9.8%, OR=1.43, 95%CI: 0.66, 3.08</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -4325,7 +4325,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>N=2 n=133; 41.5% vs. 8.6%, OR=7.49, 95%CI: 2.69, 20.84</t>
+          <t>N=2 n=133; Random-effects: 42.9% vs. 8.6%, OR=7.96, 95%CI: 2.84, 22.36; Fixed-effecs: OR=7.81, 95%CI: 2.76, 22.09</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -4372,7 +4372,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>N=1 n=303; 6.1% vs. 20.6%, OR=0.25, 95%CI: 0.12, 0.53</t>
+          <t>N=1 n=303; 5.9% vs. 20.6%, OR=0.24, 95%CI: 0.12, 0.52</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -4419,7 +4419,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>N=1 n=214; 5.5% vs. 6.8%, OR=0.81, 95%CI: 0.27, 2.48</t>
+          <t>N=1 n=214; 5.7% vs. 6.8%, OR=0.84, 95%CI: 0.26, 2.65</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -4466,7 +4466,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>N=1 n=303; 14.7% vs. 10.8%, OR=1.42, 95%CI: 0.68, 2.93</t>
+          <t>N=1 n=303; 14.9% vs. 10.8%, OR=1.45, 95%CI: 0.7, 3.03</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -4513,7 +4513,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>N=1 n=71; 8.8% vs. 2.8%, OR=3.38, 95%CI: 0.49, 23.43</t>
+          <t>N=1 n=71; 11.4% vs. 2.8%, OR=4.52, 95%CI: 0.48, 42.59</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -4560,7 +4560,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>N=1 n=214; 6.3% vs. 8.1%, OR=0.76, 95%CI: 0.27, 2.17</t>
+          <t>N=1 n=214; 6.4% vs. 8.1%, OR=0.78, 95%CI: 0.27, 2.28</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -4607,7 +4607,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>N=1 n=303; 9.7% vs. 7.8%, OR=1.26, 95%CI: 0.54, 2.91</t>
+          <t>N=1 n=303; 10% vs. 7.8%, OR=1.3, 95%CI: 0.55, 3.06</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -4654,7 +4654,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>N=1 n=62; 1.6% vs. 1.6%, OR=1, 95%CI: 0.02, 55.38</t>
+          <t>N=1 n=62; not estimable effect size 0 events in both arms</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -4701,7 +4701,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>N=2 n=133; 23.1% vs. 2.3%, OR=12.78, 95%CI: 2.29, 71.32</t>
+          <t>N=2 n=133; Random-effects: 22.8% vs. 2.3%, OR=12.62, 95%CI: 2.25, 70.79; Fixed-effecs: OR=12.6, 95%CI: 2.25, 70.72</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -4748,7 +4748,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>N=1 n=303; 7.5% vs. 4.9%, OR=1.58, 95%CI: 0.58, 4.29</t>
+          <t>N=1 n=303; 8% vs. 4.9%, OR=1.68, 95%CI: 0.6, 4.72</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -4795,7 +4795,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>N=1 n=71; 15.3% vs. 1.4%, OR=13.16, 95%CI: 0.67, 257.97</t>
+          <t>N=1 n=71; 15.3% vs. 1.4%, OR=13.16, 95%CI: 0.7, 247.71</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -4842,7 +4842,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>N=1 n=303; 3.6% vs. 11.8%, OR=0.28, 95%CI: 0.11, 0.72</t>
+          <t>N=1 n=303; 3.5% vs. 11.8%, OR=0.27, 95%CI: 0.1, 0.71</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -4879,7 +4879,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Worsening or exacerbation of schizophrenia</t>
+          <t>Worsening or exacerbation of psychosis</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -4889,7 +4889,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>N=1 n=214; 1.2% vs. 1.4%, OR=0.88, 95%CI: 0.11, 6.91</t>
+          <t>N=1 n=214; 1.4% vs. 1.4%, OR=1.06, 95%CI: 0.09, 11.86</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -4926,7 +4926,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Worsening or exacerbation of schizophrenia</t>
+          <t>Worsening or exacerbation of psychosis</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -4936,7 +4936,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>N=1 n=303; 10% vs. 5.9%, OR=1.77, 95%CI: 0.71, 4.42</t>
+          <t>N=1 n=303; 10.5% vs. 5.9%, OR=1.87, 95%CI: 0.73, 4.78</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -5030,7 +5030,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>N=1 n=104; 10% vs. 10.8%, OR=0.92, 95%CI: 0.26, 3.24</t>
+          <t>N=1 n=104; 10.4% vs. 10.8%, OR=0.96, 95%CI: 0.26, 3.53</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -5077,7 +5077,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>N=1 n=104; 0.7% vs. 1.3%, OR=0.56, 95%CI: 0.01, 29.77</t>
+          <t>N=1 n=104; not estimable effect size 0 events in both arms</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -5218,7 +5218,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>N=1 n=104; 8.7% vs. 10.8%, OR=0.79, 95%CI: 0.22, 2.85</t>
+          <t>N=1 n=104; 8.9% vs. 10.8%, OR=0.81, 95%CI: 0.21, 3.08</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -5265,7 +5265,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>N=1 n=104; 2.2% vs. 1.3%, OR=1.69, 95%CI: 0.06, 44.25</t>
+          <t>N=1 n=104; 2.2% vs. 1.3%, OR=1.69, 95%CI: 0.07, 42.58</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -5312,7 +5312,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>N=1 n=104; 20.7% vs. 24.3%, OR=0.81, 95%CI: 0.32, 2.09</t>
+          <t>N=1 n=104; 20.9% vs. 24.3%, OR=0.82, 95%CI: 0.32, 2.13</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -5359,7 +5359,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>N=1 n=104; 2.5% vs. 2.7%, OR=0.93, 95%CI: 0.12, 7.49</t>
+          <t>N=1 n=104; 3% vs. 2.7%, OR=1.11, 95%CI: 0.1, 12.64</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -5406,7 +5406,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>N=1 n=104; 0.5% vs. 2.7%, OR=0.18, 95%CI: 0.01, 4.67</t>
+          <t>N=1 n=104; 0.5% vs. 2.7%, OR=0.18, 95%CI: 0.01, 4.54</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -5453,7 +5453,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>N=1 n=104; 3% vs. 5.4%, OR=0.54, 95%CI: 0.09, 3.34</t>
+          <t>N=1 n=104; 3% vs. 5.4%, OR=0.54, 95%CI: 0.07, 3.99</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -5500,7 +5500,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>N=1 n=104; 3% vs. 5.4%, OR=0.54, 95%CI: 0.09, 3.34</t>
+          <t>N=1 n=104; 3% vs. 5.4%, OR=0.54, 95%CI: 0.07, 3.99</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -5547,7 +5547,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>N=1 n=104; 0.7% vs. 1.3%, OR=0.56, 95%CI: 0.01, 29.77</t>
+          <t>N=1 n=104; not estimable effect size 0 events in both arms</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -5594,7 +5594,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>N=1 n=104; 1.9% vs. 8.1%, OR=0.22, 95%CI: 0.03, 1.6</t>
+          <t>N=1 n=104; 1.5% vs. 8.1%, OR=0.17, 95%CI: 0.02, 1.71</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -5641,7 +5641,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>N=1 n=104; 4.6% vs. 2.7%, OR=1.72, 95%CI: 0.25, 11.7</t>
+          <t>N=1 n=104; 6% vs. 2.7%, OR=2.29, 95%CI: 0.25, 21.24</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -5688,7 +5688,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>N=1 n=104; 2.2% vs. 1.3%, OR=1.69, 95%CI: 0.06, 44.25</t>
+          <t>N=1 n=104; 2.2% vs. 1.3%, OR=1.69, 95%CI: 0.07, 42.58</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -5725,7 +5725,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Worsening or exacerbation of schizophrenia</t>
+          <t>Worsening or exacerbation of psychosis</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -5735,7 +5735,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>N=1 n=104; 0.7% vs. 1.3%, OR=0.56, 95%CI: 0.01, 29.77</t>
+          <t>N=1 n=104; not estimable effect size 0 events in both arms</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">

--- a/data_u1/meta_outcome_soe.xlsx
+++ b/data_u1/meta_outcome_soe.xlsx
@@ -518,7 +518,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>N=4 n=1291; Random-effects: SMD=0.12, 95%CI: -0.01, 0.24; Fixed-effecs: SMD=0.12, 95%CI: 0, 0.23</t>
+          <t>N=4 n=1291; Random-effects: SMD=0.13, 95%CI: 0, 0.26; Fixed-effecs: SMD=0.12, 95%CI: 0.01, 0.24</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -538,7 +538,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>No clear indication of other biases</t>
+          <t>Three trials were conducted during COVID-19 (2 in ulotaront, 1 in ralmitaront), which in some cases could be associated with factors related to smaller effect sizes. Specifically, a pooled analysis of the two Phase III ulotaront trials, using only the participants enrolled before COVID-19, showed effect sizes like the Phase II ulotaront trial. This may have underestimated the effects of TAAR1 agonists compared to placebo in favor of the latter.</t>
         </is>
       </c>
     </row>
@@ -565,7 +565,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>N=4 n=1291; Random-effects: SMD=0.15, 95%CI: -0.02, 0.32; Fixed-effecs: SMD=0.14, 95%CI: 0.02, 0.25</t>
+          <t>N=4 n=1291; Random-effects: SMD=0.16, 95%CI: -0.01, 0.33; Fixed-effecs: SMD=0.15, 95%CI: 0.04, 0.26</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -585,7 +585,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>No clear indication of other biases</t>
+          <t>Three trials were conducted during COVID-19 (2 in ulotaront, 1 in ralmitaront), which in some cases could be associated with factors related to smaller effect sizes. Specifically, a pooled analysis of the two Phase III ulotaront trials, using only the participants enrolled before COVID-19, showed effect sizes like the Phase II ulotaront trial. This may have underestimated the effects of TAAR1 agonists compared to placebo in favor of the latter.</t>
         </is>
       </c>
     </row>
@@ -1139,7 +1139,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>87.5% of eligible studies and 92.7% of participants had usable data.</t>
+          <t>77.8% of eligible studies and 91.1% of participants had usable data.</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1233,7 +1233,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>87.5% of eligible studies and 92.7% of participants had usable data.</t>
+          <t>77.8% of eligible studies and 91.1% of participants had usable data.</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1327,7 +1327,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>87.5% of eligible studies and 92.7% of participants had usable data.</t>
+          <t>77.8% of eligible studies and 91.1% of participants had usable data.</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1411,7 +1411,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>N=7 n=1451; Random-effects: 5.8% vs. 4.5%, OR=1.31, 95%CI: 0.74, 2.32; Fixed-effecs: OR=1.34, 95%CI: 0.81, 2.2</t>
+          <t>N=7 n=1451; Random-effects: 6.3% vs. 3.2%, OR=2.05, 95%CI: 1.13, 3.74; Fixed-effecs: OR=2.1, 95%CI: 1.18, 3.73</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1421,7 +1421,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>87.5% of eligible studies and 92.7% of participants had usable data.</t>
+          <t>77.8% of eligible studies and 91.1% of participants had usable data.</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1515,7 +1515,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>87.5% of eligible studies and 92.7% of participants had usable data.</t>
+          <t>77.8% of eligible studies and 91.1% of participants had usable data.</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1609,7 +1609,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>87.5% of eligible studies and 92.7% of participants had usable data.</t>
+          <t>77.8% of eligible studies and 91.1% of participants had usable data.</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>12.5% of eligible studies and 15.7% of participants had usable data.</t>
+          <t>11.1% of eligible studies and 15.4% of participants had usable data.</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -1703,7 +1703,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>25% of eligible studies and 29.3% of participants had usable data.</t>
+          <t>22.2% of eligible studies and 28.8% of participants had usable data.</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -1750,7 +1750,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>12.5% of eligible studies and 14.5% of participants had usable data.</t>
+          <t>11.1% of eligible studies and 14.2% of participants had usable data.</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -1844,7 +1844,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>37.5% of eligible studies and 73.1% of participants had usable data.</t>
+          <t>33.3% of eligible studies and 71.8% of participants had usable data.</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -1891,7 +1891,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>12.5% of eligible studies and 15.7% of participants had usable data.</t>
+          <t>11.1% of eligible studies and 15.4% of participants had usable data.</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -1938,7 +1938,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>62.5% of eligible studies and 88.5% of participants had usable data.</t>
+          <t>55.6% of eligible studies and 86.9% of participants had usable data.</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2032,7 +2032,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>62.5% of eligible studies and 88.5% of participants had usable data.</t>
+          <t>55.6% of eligible studies and 86.9% of participants had usable data.</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2126,7 +2126,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>62.5% of eligible studies and 49.5% of participants had usable data.</t>
+          <t>55.6% of eligible studies and 48.6% of participants had usable data.</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2173,7 +2173,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>87.5% of eligible studies and 92.7% of participants had usable data.</t>
+          <t>77.8% of eligible studies and 91.1% of participants had usable data.</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>75% of eligible studies and 90.2% of participants had usable data.</t>
+          <t>66.7% of eligible studies and 88.6% of participants had usable data.</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2408,7 +2408,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>12.5% of eligible studies and 15.7% of participants had usable data.</t>
+          <t>11.1% of eligible studies and 15.4% of participants had usable data.</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -2455,7 +2455,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>12.5% of eligible studies and 2.5% of participants had usable data.</t>
+          <t>11.1% of eligible studies and 2.4% of participants had usable data.</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -2549,7 +2549,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>50% of eligible studies and 33.8% of participants had usable data.</t>
+          <t>44.4% of eligible studies and 33.2% of participants had usable data.</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -2643,7 +2643,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>37.5% of eligible studies and 31.3% of participants had usable data.</t>
+          <t>33.3% of eligible studies and 30.8% of participants had usable data.</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -2690,7 +2690,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>87.5% of eligible studies and 92.7% of participants had usable data.</t>
+          <t>77.8% of eligible studies and 91.1% of participants had usable data.</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -3009,12 +3009,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>N=1 n=303; 5.2% vs. 0.5%, OR=11.24, 95%CI: 0.65, 193.78</t>
+          <t>N=1 n=303; 21.4% vs. 15.7%, OR=1.46, 95%CI: 0.78, 2.75</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>1 study with overall high risk of bias.</t>
+          <t>1 study with an overall low risk of bias.</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -4278,7 +4278,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>N=1 n=303; 13.5% vs. 9.8%, OR=1.43, 95%CI: 0.66, 3.08</t>
+          <t>N=1 n=303; 13.9% vs. 9.8%, OR=1.49, 95%CI: 0.69, 3.2</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -4936,7 +4936,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>N=1 n=303; 10.5% vs. 5.9%, OR=1.87, 95%CI: 0.73, 4.78</t>
+          <t>N=1 n=303; 14.4% vs. 5.9%, OR=2.7, 95%CI: 1.08, 6.73</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -4988,7 +4988,7 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>1 study with an overall low risk of bias.</t>
+          <t>1 study with overall high risk of bias.</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
@@ -5035,7 +5035,7 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>1 study with an overall low risk of bias.</t>
+          <t>1 study with overall high risk of bias.</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
@@ -5129,7 +5129,7 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>1 study with an overall low risk of bias.</t>
+          <t>1 study with overall high risk of bias.</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
@@ -5176,7 +5176,7 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>1 study with an overall low risk of bias.</t>
+          <t>1 study with overall high risk of bias.</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">

--- a/data_u1/meta_outcome_soe.xlsx
+++ b/data_u1/meta_outcome_soe.xlsx
@@ -471,7 +471,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>N=4 n=1357; Random-effects: 23.7% vs. 18.7%, OR=1.35, 95%CI: 0.86, 2.12; Fixed-effecs: OR=1.39, 95%CI: 1.04, 1.86</t>
+          <t>N=4 n=1357; Random-effects: 23.5% vs. 18.5%, OR=1.35, 95%CI: 0.86, 2.12; Fixed-effecs: OR=1.39, 95%CI: 1.04, 1.86</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -1082,7 +1082,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>N=2 n=93; 11.7% vs. 4.7%, OR=2.67, 95%CI: 0.48, 14.8</t>
+          <t>N=2 n=93; 8.7% vs. 3.4%, OR=2.67, 95%CI: 0.48, 14.8</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1129,7 +1129,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>N=7 n=1451; Random-effects: 23.4% vs. 19.9%, OR=1.23, 95%CI: 0.94, 1.61; Fixed-effecs: OR=1.24, 95%CI: 0.95, 1.62</t>
+          <t>N=7 n=1451; Random-effects: 23% vs. 19.5%, OR=1.23, 95%CI: 0.94, 1.61; Fixed-effecs: OR=1.24, 95%CI: 0.95, 1.62</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>N=3 n=161; 0.5% vs. 1.6%, OR=0.33, 95%CI: 0.02, 5.72</t>
+          <t>N=3 n=161; 0.3% vs. 0.8%, OR=0.33, 95%CI: 0.02, 5.72</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>N=7 n=1451; Random-effects: 9.8% vs. 6.4%, OR=1.57, 95%CI: 1.02, 2.42; Fixed-effecs: OR=1.62, 95%CI: 1.06, 2.47</t>
+          <t>N=7 n=1451; Random-effects: 9.3% vs. 6.1%, OR=1.57, 95%CI: 1.02, 2.42; Fixed-effecs: OR=1.62, 95%CI: 1.06, 2.47</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>N=4 n=177; Random-effects: 52.3% vs. 11.4%, OR=8.49, 95%CI: 1.73, 41.66; Fixed-effecs: OR=9.3, 95%CI: 3.92, 22.08</t>
+          <t>N=4 n=177; Random-effects: 48.9% vs. 10.1%, OR=8.49, 95%CI: 1.73, 41.66; Fixed-effecs: OR=9.3, 95%CI: 3.92, 22.08</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1317,7 +1317,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>N=7 n=1451; Random-effects: 42% vs. 38.9%, OR=1.14, 95%CI: 0.8, 1.63; Fixed-effecs: OR=1.21, 95%CI: 0.96, 1.52</t>
+          <t>N=7 n=1451; Random-effects: 49.7% vs. 46.5%, OR=1.14, 95%CI: 0.81, 1.61; Fixed-effecs: OR=1.22, 95%CI: 0.98, 1.52</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>N=4 n=177; Random-effects: 4.6% vs. 1.6%, OR=3.02, 95%CI: 0.36, 25.76; Fixed-effecs: OR=3.02, 95%CI: 0.36, 25.76</t>
+          <t>N=4 n=177; Random-effects: 0% vs. 0%, OR=3.02, 95%CI: 0.36, 25.76; Fixed-effecs: OR=3.02, 95%CI: 0.36, 25.76</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1411,7 +1411,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>N=7 n=1451; Random-effects: 6.3% vs. 3.2%, OR=2.05, 95%CI: 1.13, 3.74; Fixed-effecs: OR=2.1, 95%CI: 1.18, 3.73</t>
+          <t>N=7 n=1451; Random-effects: 5.6% vs. 2.8%, OR=2.05, 95%CI: 1.13, 3.74; Fixed-effecs: OR=2.1, 95%CI: 1.18, 3.73</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1505,7 +1505,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>N=7 n=1451; 3.2% vs. 1%, OR=3.15, 95%CI: 0.13, 78.11</t>
+          <t>N=7 n=1451; 0% vs. 0%, OR=3.15, 95%CI: 0.13, 78.11</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1552,7 +1552,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>N=3 n=161; Random-effects: 19.5% vs. 1.6%, OR=15.14, 95%CI: 3.71, 61.75; Fixed-effecs: OR=15.14, 95%CI: 3.71, 61.75</t>
+          <t>N=3 n=161; Random-effects: 10.8% vs. 0.8%, OR=15.14, 95%CI: 3.71, 61.75; Fixed-effecs: OR=15.14, 95%CI: 3.71, 61.75</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1599,7 +1599,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>N=7 n=1451; Random-effects: 5.6% vs. 4.5%, OR=1.24, 95%CI: 0.73, 2.11; Fixed-effecs: OR=1.31, 95%CI: 0.79, 2.17</t>
+          <t>N=7 n=1451; Random-effects: 4.5% vs. 3.7%, OR=1.24, 95%CI: 0.73, 2.11; Fixed-effecs: OR=1.31, 95%CI: 0.79, 2.17</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1881,7 +1881,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>N=1 n=245; 1.2% vs. 0.4%, OR=3.15, 95%CI: 0.13, 78.11</t>
+          <t>N=1 n=245; 0% vs. 0%, OR=3.15, 95%CI: 0.13, 78.11</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1928,7 +1928,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>N=5 n=1385; Random-effects: 5.5% vs. 4.7%, OR=1.19, 95%CI: 0.71, 1.99; Fixed-effecs: OR=1.21, 95%CI: 0.72, 2.01</t>
+          <t>N=5 n=1385; Random-effects: 5.3% vs. 4.5%, OR=1.19, 95%CI: 0.71, 1.99; Fixed-effecs: OR=1.21, 95%CI: 0.72, 2.01</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -2022,7 +2022,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>N=5 n=1385; Random-effects: 5.2% vs. 5.8%, OR=0.89, 95%CI: 0.3, 2.64; Fixed-effecs: OR=1.17, 95%CI: 0.73, 1.89</t>
+          <t>N=5 n=1385; Random-effects: 4.9% vs. 5.5%, OR=0.89, 95%CI: 0.3, 2.64; Fixed-effecs: OR=1.17, 95%CI: 0.73, 1.89</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -2069,7 +2069,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>N=3 n=161; Random-effects: 28.8% vs. 4.1%, OR=9.55, 95%CI: 3.5, 26.09; Fixed-effecs: OR=9.55, 95%CI: 3.5, 26.09</t>
+          <t>N=3 n=161; Random-effects: 5.6% vs. 0.6%, OR=9.55, 95%CI: 3.5, 26.09; Fixed-effecs: OR=9.55, 95%CI: 3.5, 26.09</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -2116,7 +2116,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>N=5 n=774; Random-effects: 5.5% vs. 4.7%, OR=1.18, 95%CI: 0.47, 2.99; Fixed-effecs: OR=1.19, 95%CI: 0.48, 2.98</t>
+          <t>N=5 n=774; Random-effects: 1.6% vs. 1.4%, OR=1.18, 95%CI: 0.47, 2.99; Fixed-effecs: OR=1.19, 95%CI: 0.48, 2.98</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -2163,7 +2163,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>N=7 n=1451; Random-effects: 8.5% vs. 7.4%, OR=1.16, 95%CI: 0.57, 2.34; Fixed-effecs: OR=1.15, 95%CI: 0.75, 1.76</t>
+          <t>N=7 n=1451; Random-effects: 7.4% vs. 6.5%, OR=1.16, 95%CI: 0.57, 2.34; Fixed-effecs: OR=1.15, 95%CI: 0.75, 1.76</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -2257,7 +2257,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>N=6 n=1412; Random-effects: 10.7% vs. 8.5%, OR=1.29, 95%CI: 0.86, 1.95; Fixed-effecs: OR=1.32, 95%CI: 0.89, 1.94</t>
+          <t>N=6 n=1412; Random-effects: 10.3% vs. 8.2%, OR=1.29, 95%CI: 0.86, 1.95; Fixed-effecs: OR=1.32, 95%CI: 0.89, 1.94</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>N=2 n=92; 8.1% vs. 1.6%, OR=5.32, 95%CI: 0.6, 46.78</t>
+          <t>N=2 n=92; 5.5% vs. 1.1%, OR=5.32, 95%CI: 0.6, 46.78</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -2492,7 +2492,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>N=2 n=137; Random-effects: 19.9% vs. 3.5%, OR=6.89, 95%CI: 1.98, 23.92; Fixed-effecs: OR=6.89, 95%CI: 1.98, 23.92</t>
+          <t>N=2 n=137; Random-effects: 17.3% vs. 2.9%, OR=6.89, 95%CI: 1.98, 23.92; Fixed-effecs: OR=6.89, 95%CI: 1.98, 23.92</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2539,7 +2539,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>N=4 n=529; Random-effects: 6.2% vs. 2.9%, OR=2.23, 95%CI: 0.34, 14.68; Fixed-effecs: OR=2.24, 95%CI: 0.34, 14.7</t>
+          <t>N=4 n=529; Random-effects: 0.8% vs. 0.3%, OR=2.23, 95%CI: 0.34, 14.68; Fixed-effecs: OR=2.24, 95%CI: 0.34, 14.7</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>N=1 n=69; 15.3% vs. 1.4%, OR=12.44, 95%CI: 0.66, 234.38</t>
+          <t>N=1 n=69; 0% vs. 0%, OR=12.44, 95%CI: 0.66, 234.38</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2633,7 +2633,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>N=3 n=490; Random-effects: 3.3% vs. 2.6%, OR=1.28, 95%CI: 0.15, 11.23; Fixed-effecs: OR=1.39, 95%CI: 0.18, 10.67</t>
+          <t>N=3 n=490; Random-effects: 0.5% vs. 0.4%, OR=1.28, 95%CI: 0.15, 11.23; Fixed-effecs: OR=1.39, 95%CI: 0.18, 10.67</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2680,7 +2680,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>N=7 n=1451; Random-effects: 7.4% vs. 4.9%, OR=1.57, 95%CI: 0.86, 2.9; Fixed-effecs: OR=1.75, 95%CI: 1.09, 2.83</t>
+          <t>N=7 n=1451; Random-effects: 8.8% vs. 5.2%, OR=1.76, 95%CI: 1.01, 3.08; Fixed-effecs: OR=1.98, 95%CI: 1.27, 3.06</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -3338,7 +3338,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>N=2 n=133; Random-effects: 87.2% vs. 36%, OR=12.17, 95%CI: 1.22, 121.04; Fixed-effecs: OR=9.49, 95%CI: 3.94, 22.84</t>
+          <t>N=2 n=133; Random-effects: 87.2% vs. 35.8%, OR=12.17, 95%CI: 1.22, 121.04; Fixed-effecs: OR=9.49, 95%CI: 3.94, 22.84</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>N=2 n=133; 4.5% vs. 1.5%, OR=3.17, 95%CI: 0.13, 80.58</t>
+          <t>N=2 n=133; 0% vs. 0%, OR=3.17, 95%CI: 0.13, 80.58</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -3526,7 +3526,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>N=1 n=214; 2.5% vs. 0.7%, OR=3.79, 95%CI: 0.19, 74.42</t>
+          <t>N=1 n=214; 0% vs. 0%, OR=3.79, 95%CI: 0.19, 74.42</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -3573,7 +3573,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>N=1 n=303; 8.2% vs. 0.5%, OR=18.23, 95%CI: 1.08, 307.1</t>
+          <t>N=1 n=303; 0% vs. 0%, OR=18.23, 95%CI: 1.08, 307.1</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -3761,7 +3761,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>N=2 n=133; Random-effects: 30.5% vs. 1.5%, OR=29.82, 95%CI: 3.87, 229.8; Fixed-effecs: OR=30.28, 95%CI: 3.95, 231.96</t>
+          <t>N=2 n=133; Random-effects: 0% vs. 0%, OR=29.82, 95%CI: 3.87, 229.8; Fixed-effecs: OR=30.28, 95%CI: 3.95, 231.96</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -4137,7 +4137,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>N=1 n=214; 6% vs. 0.7%, OR=9.56, 95%CI: 0.54, 167.96</t>
+          <t>N=1 n=214; 0% vs. 0%, OR=9.56, 95%CI: 0.54, 167.96</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -4325,7 +4325,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>N=2 n=133; Random-effects: 42.9% vs. 8.6%, OR=7.96, 95%CI: 2.84, 22.36; Fixed-effecs: OR=7.81, 95%CI: 2.76, 22.09</t>
+          <t>N=2 n=133; Random-effects: 43.1% vs. 8.7%, OR=7.96, 95%CI: 2.84, 22.36; Fixed-effecs: OR=7.81, 95%CI: 2.76, 22.09</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -4701,7 +4701,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>N=2 n=133; Random-effects: 22.8% vs. 2.3%, OR=12.62, 95%CI: 2.25, 70.79; Fixed-effecs: OR=12.6, 95%CI: 2.25, 70.72</t>
+          <t>N=2 n=133; Random-effects: 16.1% vs. 1.5%, OR=12.62, 95%CI: 2.25, 70.79; Fixed-effecs: OR=12.6, 95%CI: 2.25, 70.72</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -4795,7 +4795,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>N=1 n=71; 15.3% vs. 1.4%, OR=13.16, 95%CI: 0.7, 247.71</t>
+          <t>N=1 n=71; 0% vs. 0%, OR=13.16, 95%CI: 0.7, 247.71</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -4889,7 +4889,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>N=1 n=214; 1.4% vs. 1.4%, OR=1.06, 95%CI: 0.09, 11.86</t>
+          <t>N=1 n=214; 2.1% vs. 1.4%, OR=1.6, 95%CI: 0.16, 15.64</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -5265,7 +5265,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>N=1 n=104; 2.2% vs. 1.3%, OR=1.69, 95%CI: 0.07, 42.58</t>
+          <t>N=1 n=104; 0% vs. 0%, OR=1.69, 95%CI: 0.07, 42.58</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -5688,7 +5688,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>N=1 n=104; 2.2% vs. 1.3%, OR=1.69, 95%CI: 0.07, 42.58</t>
+          <t>N=1 n=104; 0% vs. 0%, OR=1.69, 95%CI: 0.07, 42.58</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">

--- a/data_u1/meta_outcome_soe.xlsx
+++ b/data_u1/meta_outcome_soe.xlsx
@@ -706,7 +706,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>N=1 n=27; 2.7% vs. 6.7%, OR=0.39, 95%CI: 0.01, 10.37</t>
+          <t>N=1 n=27; 7.5% vs. 6.7%, OR=0.39, 95%CI: 0.01, 10.37</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>N=3 n=161; 0.3% vs. 0.8%, OR=0.33, 95%CI: 0.02, 5.72</t>
+          <t>N=3 n=161; 0.3% vs. 0.8%, OR=0.33, 95%CI: 0.02, 6.09</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>N=4 n=177; Random-effects: 0% vs. 0%, OR=3.02, 95%CI: 0.36, 25.76; Fixed-effecs: OR=3.02, 95%CI: 0.36, 25.76</t>
+          <t>N=4 n=177; Random-effects: 4% vs. 0%, OR=3.02, 95%CI: 0.35, 26.43; Fixed-effecs: OR=3.02, 95%CI: 0.35, 26.43</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1505,7 +1505,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>N=7 n=1451; 0% vs. 0%, OR=3.15, 95%CI: 0.13, 78.11</t>
+          <t>N=7 n=1451; 2% vs. 0%, OR=3.15, 95%CI: 0.13, 78.11</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1552,7 +1552,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>N=3 n=161; Random-effects: 10.8% vs. 0.8%, OR=15.14, 95%CI: 3.71, 61.75; Fixed-effecs: OR=15.14, 95%CI: 3.71, 61.75</t>
+          <t>N=3 n=161; Random-effects: 10.9% vs. 0.8%, OR=15.34, 95%CI: 3.74, 62.92; Fixed-effecs: OR=15.34, 95%CI: 3.74, 62.92</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1881,7 +1881,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>N=1 n=245; 0% vs. 0%, OR=3.15, 95%CI: 0.13, 78.11</t>
+          <t>N=1 n=245; 1.2% vs. 0%, OR=3.15, 95%CI: 0.13, 78.11</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -2069,7 +2069,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>N=3 n=161; Random-effects: 5.6% vs. 0.6%, OR=9.55, 95%CI: 3.5, 26.09; Fixed-effecs: OR=9.55, 95%CI: 3.5, 26.09</t>
+          <t>N=3 n=161; Random-effects: 5.6% vs. 0.6%, OR=9.6, 95%CI: 3.51, 26.27; Fixed-effecs: OR=9.6, 95%CI: 3.51, 26.27</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>N=1 n=69; 0% vs. 0%, OR=12.44, 95%CI: 0.66, 234.38</t>
+          <t>N=1 n=69; 15.3% vs. 0%, OR=12.44, 95%CI: 0.66, 234.38</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -3338,7 +3338,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>N=2 n=133; Random-effects: 87.2% vs. 35.8%, OR=12.17, 95%CI: 1.22, 121.04; Fixed-effecs: OR=9.49, 95%CI: 3.94, 22.84</t>
+          <t>N=2 n=102; Random-effects: 87% vs. 35.8%, OR=12.02, 95%CI: 1.21, 119.07; Fixed-effecs: OR=6.69, 95%CI: 2.8, 15.96</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -3353,7 +3353,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>50% studies and 46.6% participants with schizophrenia.</t>
+          <t>50% studies and 30.4% participants with schizophrenia.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>N=2 n=133; 0% vs. 0%, OR=3.17, 95%CI: 0.13, 80.58</t>
+          <t>N=2 n=102; 4.5% vs. 0%, OR=3.17, 95%CI: 0.13, 80.58</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -3494,7 +3494,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>50% studies and 46.6% participants with schizophrenia.</t>
+          <t>50% studies and 30.4% participants with schizophrenia.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -3526,7 +3526,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>N=1 n=214; 0% vs. 0%, OR=3.79, 95%CI: 0.19, 74.42</t>
+          <t>N=1 n=214; 2.5% vs. 0%, OR=3.79, 95%CI: 0.19, 74.42</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -3573,7 +3573,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>N=1 n=303; 0% vs. 0%, OR=18.23, 95%CI: 1.08, 307.1</t>
+          <t>N=1 n=303; 8.2% vs. 0%, OR=18.23, 95%CI: 1.08, 307.1</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -3620,7 +3620,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>N=2 n=133; not estimable effect size 0 events in both arms</t>
+          <t>N=2 n=102; not estimable effect size 0 events in both arms</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -3635,7 +3635,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>50% studies and 46.6% participants with schizophrenia.</t>
+          <t>50% studies and 30.4% participants with schizophrenia.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -3761,7 +3761,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>N=2 n=133; Random-effects: 0% vs. 0%, OR=29.82, 95%CI: 3.87, 229.8; Fixed-effecs: OR=30.28, 95%CI: 3.95, 231.96</t>
+          <t>N=2 n=102; Random-effects: 30.2% vs. 0%, OR=29.38, 95%CI: 4.04, 213.55; Fixed-effecs: OR=29.38, 95%CI: 4.04, 213.55</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>50% studies and 46.6% participants with schizophrenia.</t>
+          <t>50% studies and 30.4% participants with schizophrenia.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -4137,7 +4137,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>N=1 n=214; 0% vs. 0%, OR=9.56, 95%CI: 0.54, 167.96</t>
+          <t>N=1 n=214; 6% vs. 0%, OR=9.56, 95%CI: 0.54, 167.96</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -4325,7 +4325,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>N=2 n=133; Random-effects: 43.1% vs. 8.7%, OR=7.96, 95%CI: 2.84, 22.36; Fixed-effecs: OR=7.81, 95%CI: 2.76, 22.09</t>
+          <t>N=2 n=102; Random-effects: 42.5% vs. 8.7%, OR=7.78, 95%CI: 2.83, 21.4; Fixed-effecs: OR=7.78, 95%CI: 2.83, 21.4</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -4340,7 +4340,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>50% studies and 46.6% participants with schizophrenia.</t>
+          <t>50% studies and 30.4% participants with schizophrenia.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -4654,7 +4654,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>N=1 n=62; not estimable effect size 0 events in both arms</t>
+          <t>N=1 n=31; not estimable effect size 0 events in both arms</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -4664,7 +4664,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>50% of eligible studies and 61.4% of participants had usable data.</t>
+          <t>50% of eligible studies and 30.7% of participants had usable data.</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -4701,7 +4701,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>N=2 n=133; Random-effects: 16.1% vs. 1.5%, OR=12.62, 95%CI: 2.25, 70.79; Fixed-effecs: OR=12.6, 95%CI: 2.25, 70.72</t>
+          <t>N=2 n=102; Random-effects: 15.9% vs. 1.5%, OR=12.5, 95%CI: 2.33, 67.21; Fixed-effecs: OR=12.5, 95%CI: 2.33, 67.21</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -4716,7 +4716,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>50% studies and 46.6% participants with schizophrenia.</t>
+          <t>50% studies and 30.4% participants with schizophrenia.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -4795,7 +4795,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>N=1 n=71; 0% vs. 0%, OR=13.16, 95%CI: 0.7, 247.71</t>
+          <t>N=1 n=71; 15.3% vs. 0%, OR=13.16, 95%CI: 0.7, 247.71</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -5265,7 +5265,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>N=1 n=104; 0% vs. 0%, OR=1.69, 95%CI: 0.07, 42.58</t>
+          <t>N=1 n=104; 2.2% vs. 0%, OR=1.69, 95%CI: 0.07, 42.58</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -5688,7 +5688,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>N=1 n=104; 0% vs. 0%, OR=1.69, 95%CI: 0.07, 42.58</t>
+          <t>N=1 n=104; 2.2% vs. 0%, OR=1.69, 95%CI: 0.07, 42.58</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">

--- a/data_u1/meta_outcome_soe.xlsx
+++ b/data_u1/meta_outcome_soe.xlsx
@@ -706,7 +706,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>N=1 n=27; 7.5% vs. 6.7%, OR=0.39, 95%CI: 0.01, 10.37</t>
+          <t>N=1 n=27; 7.8% vs. 6.7%, OR=0.39, 95%CI: 0.01, 10.37</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1082,7 +1082,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>N=2 n=93; 8.7% vs. 3.4%, OR=2.67, 95%CI: 0.48, 14.8</t>
+          <t>N=2 n=93; 11.7% vs. 3.4%, OR=2.67, 95%CI: 0.48, 14.8</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>N=3 n=161; 0.3% vs. 0.8%, OR=0.33, 95%CI: 0.02, 6.09</t>
+          <t>N=3 n=161; 0.5% vs. 0.8%, OR=0.33, 95%CI: 0.02, 6.09</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>N=7 n=1451; Random-effects: 9.3% vs. 6.1%, OR=1.57, 95%CI: 1.02, 2.42; Fixed-effecs: OR=1.62, 95%CI: 1.06, 2.47</t>
+          <t>N=7 n=1451; Random-effects: 9.8% vs. 6.1%, OR=1.57, 95%CI: 1.02, 2.42; Fixed-effecs: OR=1.62, 95%CI: 1.06, 2.47</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>N=4 n=177; Random-effects: 4% vs. 0%, OR=3.02, 95%CI: 0.35, 26.43; Fixed-effecs: OR=3.02, 95%CI: 0.35, 26.43</t>
+          <t>N=4 n=177; Random-effects: 4.6% vs. 0%, OR=3.02, 95%CI: 0.35, 26.43; Fixed-effecs: OR=3.02, 95%CI: 0.35, 26.43</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1411,7 +1411,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>N=7 n=1451; Random-effects: 5.6% vs. 2.8%, OR=2.05, 95%CI: 1.13, 3.74; Fixed-effecs: OR=2.1, 95%CI: 1.18, 3.73</t>
+          <t>N=7 n=1451; Random-effects: 6.3% vs. 2.8%, OR=2.05, 95%CI: 1.13, 3.74; Fixed-effecs: OR=2.1, 95%CI: 1.18, 3.73</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1505,7 +1505,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>N=7 n=1451; 2% vs. 0%, OR=3.15, 95%CI: 0.13, 78.11</t>
+          <t>N=7 n=1451; 3.2% vs. 0%, OR=3.15, 95%CI: 0.13, 78.11</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1552,7 +1552,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>N=3 n=161; Random-effects: 10.9% vs. 0.8%, OR=15.34, 95%CI: 3.74, 62.92; Fixed-effecs: OR=15.34, 95%CI: 3.74, 62.92</t>
+          <t>N=3 n=161; Random-effects: 19.7% vs. 0.8%, OR=15.34, 95%CI: 3.74, 62.92; Fixed-effecs: OR=15.34, 95%CI: 3.74, 62.92</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1599,7 +1599,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>N=7 n=1451; Random-effects: 4.5% vs. 3.7%, OR=1.24, 95%CI: 0.73, 2.11; Fixed-effecs: OR=1.31, 95%CI: 0.79, 2.17</t>
+          <t>N=7 n=1451; Random-effects: 5.6% vs. 3.7%, OR=1.24, 95%CI: 0.73, 2.11; Fixed-effecs: OR=1.31, 95%CI: 0.79, 2.17</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1928,7 +1928,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>N=5 n=1385; Random-effects: 5.3% vs. 4.5%, OR=1.19, 95%CI: 0.71, 1.99; Fixed-effecs: OR=1.21, 95%CI: 0.72, 2.01</t>
+          <t>N=5 n=1385; Random-effects: 5.5% vs. 4.5%, OR=1.19, 95%CI: 0.71, 1.99; Fixed-effecs: OR=1.21, 95%CI: 0.72, 2.01</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -2022,7 +2022,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>N=5 n=1385; Random-effects: 4.9% vs. 5.5%, OR=0.89, 95%CI: 0.3, 2.64; Fixed-effecs: OR=1.17, 95%CI: 0.73, 1.89</t>
+          <t>N=5 n=1385; Random-effects: 5.2% vs. 5.5%, OR=0.89, 95%CI: 0.3, 2.64; Fixed-effecs: OR=1.17, 95%CI: 0.73, 1.89</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -2069,7 +2069,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>N=3 n=161; Random-effects: 5.6% vs. 0.6%, OR=9.6, 95%CI: 3.51, 26.27; Fixed-effecs: OR=9.6, 95%CI: 3.51, 26.27</t>
+          <t>N=3 n=161; Random-effects: 28.9% vs. 0.6%, OR=9.6, 95%CI: 3.51, 26.27; Fixed-effecs: OR=9.6, 95%CI: 3.51, 26.27</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -2116,7 +2116,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>N=5 n=774; Random-effects: 1.6% vs. 1.4%, OR=1.18, 95%CI: 0.47, 2.99; Fixed-effecs: OR=1.19, 95%CI: 0.48, 2.98</t>
+          <t>N=5 n=774; Random-effects: 5.5% vs. 1.4%, OR=1.18, 95%CI: 0.47, 2.99; Fixed-effecs: OR=1.19, 95%CI: 0.48, 2.98</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -2163,7 +2163,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>N=7 n=1451; Random-effects: 7.4% vs. 6.5%, OR=1.16, 95%CI: 0.57, 2.34; Fixed-effecs: OR=1.15, 95%CI: 0.75, 1.76</t>
+          <t>N=7 n=1451; Random-effects: 8.5% vs. 6.5%, OR=1.16, 95%CI: 0.57, 2.34; Fixed-effecs: OR=1.15, 95%CI: 0.75, 1.76</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -2257,7 +2257,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>N=6 n=1412; Random-effects: 10.3% vs. 8.2%, OR=1.29, 95%CI: 0.86, 1.95; Fixed-effecs: OR=1.32, 95%CI: 0.89, 1.94</t>
+          <t>N=6 n=1412; Random-effects: 10.7% vs. 8.2%, OR=1.29, 95%CI: 0.86, 1.95; Fixed-effecs: OR=1.32, 95%CI: 0.89, 1.94</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>N=2 n=92; 5.5% vs. 1.1%, OR=5.32, 95%CI: 0.6, 46.78</t>
+          <t>N=2 n=92; 8.1% vs. 1.1%, OR=5.32, 95%CI: 0.6, 46.78</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -2492,7 +2492,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>N=2 n=137; Random-effects: 17.3% vs. 2.9%, OR=6.89, 95%CI: 1.98, 23.92; Fixed-effecs: OR=6.89, 95%CI: 1.98, 23.92</t>
+          <t>N=2 n=137; Random-effects: 19.9% vs. 2.9%, OR=6.89, 95%CI: 1.98, 23.92; Fixed-effecs: OR=6.89, 95%CI: 1.98, 23.92</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2539,7 +2539,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>N=4 n=529; Random-effects: 0.8% vs. 0.3%, OR=2.23, 95%CI: 0.34, 14.68; Fixed-effecs: OR=2.24, 95%CI: 0.34, 14.7</t>
+          <t>N=4 n=529; Random-effects: 6.2% vs. 0.3%, OR=2.23, 95%CI: 0.34, 14.68; Fixed-effecs: OR=2.24, 95%CI: 0.34, 14.7</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2633,7 +2633,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>N=3 n=490; Random-effects: 0.5% vs. 0.4%, OR=1.28, 95%CI: 0.15, 11.23; Fixed-effecs: OR=1.39, 95%CI: 0.18, 10.67</t>
+          <t>N=3 n=490; Random-effects: 3.3% vs. 0.4%, OR=1.28, 95%CI: 0.15, 11.23; Fixed-effecs: OR=1.39, 95%CI: 0.18, 10.67</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2680,7 +2680,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>N=7 n=1451; Random-effects: 8.8% vs. 5.2%, OR=1.76, 95%CI: 1.01, 3.08; Fixed-effecs: OR=1.98, 95%CI: 1.27, 3.06</t>
+          <t>N=7 n=1451; Random-effects: 9.3% vs. 5.2%, OR=1.76, 95%CI: 1.01, 3.08; Fixed-effecs: OR=1.98, 95%CI: 1.27, 3.06</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -4325,7 +4325,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>N=2 n=102; Random-effects: 42.5% vs. 8.7%, OR=7.78, 95%CI: 2.83, 21.4; Fixed-effecs: OR=7.78, 95%CI: 2.83, 21.4</t>
+          <t>N=2 n=102; Random-effects: 42.4% vs. 8.7%, OR=7.78, 95%CI: 2.83, 21.4; Fixed-effecs: OR=7.78, 95%CI: 2.83, 21.4</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -4701,7 +4701,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>N=2 n=102; Random-effects: 15.9% vs. 1.5%, OR=12.5, 95%CI: 2.33, 67.21; Fixed-effecs: OR=12.5, 95%CI: 2.33, 67.21</t>
+          <t>N=2 n=102; Random-effects: 22.7% vs. 1.5%, OR=12.5, 95%CI: 2.33, 67.21; Fixed-effecs: OR=12.5, 95%CI: 2.33, 67.21</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">

--- a/data_u1/meta_outcome_soe.xlsx
+++ b/data_u1/meta_outcome_soe.xlsx
@@ -1411,7 +1411,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>N=7 n=1451; Random-effects: 6.3% vs. 2.8%, OR=2.05, 95%CI: 1.13, 3.74; Fixed-effecs: OR=2.1, 95%CI: 1.18, 3.73</t>
+          <t>N=7 n=1451; Random-effects: 6.3% vs. 2.8%, OR=2.05, 95%CI: 1.13, 3.74; Fixed-effecs: OR=2.17, 95%CI: 1.2, 3.91</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1599,7 +1599,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>N=7 n=1451; Random-effects: 5.6% vs. 3.7%, OR=1.24, 95%CI: 0.73, 2.11; Fixed-effecs: OR=1.31, 95%CI: 0.79, 2.17</t>
+          <t>N=7 n=1451; Random-effects: 5.6% vs. 3.7%, OR=1.24, 95%CI: 0.73, 2.11; Fixed-effecs: OR=1.32, 95%CI: 0.79, 2.21</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1928,7 +1928,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>N=5 n=1385; Random-effects: 5.5% vs. 4.5%, OR=1.19, 95%CI: 0.71, 1.99; Fixed-effecs: OR=1.21, 95%CI: 0.72, 2.01</t>
+          <t>N=5 n=1385; Random-effects: 5.5% vs. 4.5%, OR=1.19, 95%CI: 0.71, 1.99; Fixed-effecs: OR=1.22, 95%CI: 0.73, 2.04</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -2116,7 +2116,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>N=5 n=774; Random-effects: 5.5% vs. 1.4%, OR=1.18, 95%CI: 0.47, 2.99; Fixed-effecs: OR=1.19, 95%CI: 0.48, 2.98</t>
+          <t>N=5 n=774; Random-effects: 5.5% vs. 1.4%, OR=1.18, 95%CI: 0.47, 2.99; Fixed-effecs: OR=1.24, 95%CI: 0.48, 3.18</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -2539,7 +2539,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>N=4 n=529; Random-effects: 6.2% vs. 0.3%, OR=2.23, 95%CI: 0.34, 14.68; Fixed-effecs: OR=2.24, 95%CI: 0.34, 14.7</t>
+          <t>N=4 n=529; Random-effects: 6.2% vs. 0.3%, OR=2.23, 95%CI: 0.34, 14.68; Fixed-effecs: OR=3.14, 95%CI: 0.33, 29.62</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2633,7 +2633,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>N=3 n=490; Random-effects: 3.3% vs. 0.4%, OR=1.28, 95%CI: 0.15, 11.23; Fixed-effecs: OR=1.39, 95%CI: 0.18, 10.67</t>
+          <t>N=3 n=490; Random-effects: 3.3% vs. 0.4%, OR=1.28, 95%CI: 0.15, 11.23; Fixed-effecs: OR=1.44, 95%CI: 0.14, 15.03</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2680,7 +2680,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>N=7 n=1451; Random-effects: 9.3% vs. 5.2%, OR=1.76, 95%CI: 1.01, 3.08; Fixed-effecs: OR=1.98, 95%CI: 1.27, 3.06</t>
+          <t>N=7 n=1451; Random-effects: 9.3% vs. 5.2%, OR=1.76, 95%CI: 1.01, 3.08; Fixed-effecs: OR=2.01, 95%CI: 1.29, 3.14</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">

--- a/data_u1/meta_outcome_soe.xlsx
+++ b/data_u1/meta_outcome_soe.xlsx
@@ -471,7 +471,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>N=4 n=1357; Random-effects: 23.5% vs. 18.5%, OR=1.35, 95%CI: 0.86, 2.12; Fixed-effecs: OR=1.39, 95%CI: 1.04, 1.86</t>
+          <t>N=4 n=1357; Random-effects: 23.5% vs. 18.5%, OR=1.35, 95%CI: 0.68, 2.68; Fixed-effecs: OR=1.39, 95%CI: 1.04, 1.86</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -1129,7 +1129,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>N=7 n=1451; Random-effects: 23% vs. 19.5%, OR=1.23, 95%CI: 0.94, 1.61; Fixed-effecs: OR=1.24, 95%CI: 0.95, 1.62</t>
+          <t>N=7 n=1451; Random-effects: 23% vs. 19.5%, OR=1.23, 95%CI: 1, 1.52; Fixed-effecs: OR=1.24, 95%CI: 0.95, 1.62</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>N=7 n=1451; Random-effects: 9.8% vs. 6.1%, OR=1.57, 95%CI: 1.02, 2.42; Fixed-effecs: OR=1.62, 95%CI: 1.06, 2.47</t>
+          <t>N=7 n=1451; Random-effects: 9.8% vs. 6.1%, OR=1.57, 95%CI: 0.94, 2.61; Fixed-effecs: OR=1.62, 95%CI: 1.06, 2.47</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1317,7 +1317,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>N=7 n=1451; Random-effects: 49.7% vs. 46.5%, OR=1.14, 95%CI: 0.81, 1.61; Fixed-effecs: OR=1.22, 95%CI: 0.98, 1.52</t>
+          <t>N=7 n=1451; Random-effects: 49.7% vs. 46.5%, OR=1.14, 95%CI: 0.73, 1.78; Fixed-effecs: OR=1.22, 95%CI: 0.98, 1.52</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1411,7 +1411,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>N=7 n=1451; Random-effects: 6.3% vs. 2.8%, OR=2.05, 95%CI: 1.13, 3.74; Fixed-effecs: OR=2.17, 95%CI: 1.2, 3.91</t>
+          <t>N=7 n=1451; Random-effects: 6.3% vs. 2.8%, OR=2.05, 95%CI: 1.08, 3.91; Fixed-effecs: OR=2.17, 95%CI: 1.2, 3.91</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1505,7 +1505,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>N=7 n=1451; 3.2% vs. 0%, OR=3.15, 95%CI: 0.13, 78.11</t>
+          <t>N=7 n=1451; 3.2% vs. 0%, OR=3.15, 95%CI: 0.13, 78.1</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1599,7 +1599,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>N=7 n=1451; Random-effects: 5.6% vs. 3.7%, OR=1.24, 95%CI: 0.73, 2.11; Fixed-effecs: OR=1.32, 95%CI: 0.79, 2.21</t>
+          <t>N=7 n=1451; Random-effects: 5.6% vs. 3.7%, OR=1.24, 95%CI: 0.61, 2.53; Fixed-effecs: OR=1.32, 95%CI: 0.79, 2.21</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1881,7 +1881,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>N=1 n=245; 1.2% vs. 0%, OR=3.15, 95%CI: 0.13, 78.11</t>
+          <t>N=1 n=245; 1.2% vs. 0%, OR=3.15, 95%CI: 0.13, 78.1</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -2163,7 +2163,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>N=7 n=1451; Random-effects: 8.5% vs. 6.5%, OR=1.16, 95%CI: 0.57, 2.34; Fixed-effecs: OR=1.15, 95%CI: 0.75, 1.76</t>
+          <t>N=7 n=1451; Random-effects: 8.5% vs. 6.5%, OR=1.16, 95%CI: 0.47, 2.84; Fixed-effecs: OR=1.15, 95%CI: 0.75, 1.76</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>N=1 n=69; 15.3% vs. 0%, OR=12.44, 95%CI: 0.66, 234.38</t>
+          <t>N=1 n=69; 15.3% vs. 0%, OR=12.44, 95%CI: 0.66, 234.37</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2680,7 +2680,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>N=7 n=1451; Random-effects: 9.3% vs. 5.2%, OR=1.76, 95%CI: 1.01, 3.08; Fixed-effecs: OR=2.01, 95%CI: 1.29, 3.14</t>
+          <t>N=7 n=1451; Random-effects: 9.3% vs. 5.2%, OR=1.76, 95%CI: 0.92, 3.37; Fixed-effecs: OR=2.01, 95%CI: 1.29, 3.14</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -3244,7 +3244,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>N=1 n=214; 6.4% vs. 1.4%, OR=5.02, 95%CI: 0.62, 40.38</t>
+          <t>N=1 n=214; 6.4% vs. 1.4%, OR=5.02, 95%CI: 0.62, 40.37</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -3338,7 +3338,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>N=2 n=102; Random-effects: 87% vs. 35.8%, OR=12.02, 95%CI: 1.21, 119.07; Fixed-effecs: OR=6.69, 95%CI: 2.8, 15.96</t>
+          <t>N=2 n=102; Random-effects: 87% vs. 35.8%, OR=12.02, 95%CI: 1.21, 119.06; Fixed-effecs: OR=6.69, 95%CI: 2.8, 15.96</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -3526,7 +3526,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>N=1 n=214; 2.5% vs. 0%, OR=3.79, 95%CI: 0.19, 74.42</t>
+          <t>N=1 n=214; 2.5% vs. 0%, OR=3.79, 95%CI: 0.19, 74.41</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -3573,7 +3573,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>N=1 n=303; 8.2% vs. 0%, OR=18.23, 95%CI: 1.08, 307.1</t>
+          <t>N=1 n=303; 8.2% vs. 0%, OR=18.23, 95%CI: 1.08, 307.09</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -3761,7 +3761,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>N=2 n=102; Random-effects: 30.2% vs. 0%, OR=29.38, 95%CI: 4.04, 213.55; Fixed-effecs: OR=29.38, 95%CI: 4.04, 213.55</t>
+          <t>N=2 n=102; Random-effects: 30.2% vs. 0%, OR=29.38, 95%CI: 4.04, 213.54; Fixed-effecs: OR=29.38, 95%CI: 4.04, 213.54</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -4137,7 +4137,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>N=1 n=214; 6% vs. 0%, OR=9.56, 95%CI: 0.54, 167.96</t>
+          <t>N=1 n=214; 6% vs. 0%, OR=9.56, 95%CI: 0.54, 167.95</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -4795,7 +4795,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>N=1 n=71; 15.3% vs. 0%, OR=13.16, 95%CI: 0.7, 247.71</t>
+          <t>N=1 n=71; 15.3% vs. 0%, OR=13.16, 95%CI: 0.7, 247.69</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">

--- a/data_u1/meta_outcome_soe.xlsx
+++ b/data_u1/meta_outcome_soe.xlsx
@@ -706,7 +706,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>N=1 n=27; 7.8% vs. 6.7%, OR=0.39, 95%CI: 0.01, 10.37</t>
+          <t>N=1 n=27; 2.7% vs. 6.7%, OR=0.39, 95%CI: 0.01, 10.37</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1082,7 +1082,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>N=2 n=93; 11.7% vs. 3.4%, OR=2.67, 95%CI: 0.48, 14.8</t>
+          <t>N=2 n=93; 8.7% vs. 3.4%, OR=2.67, 95%CI: 0.48, 14.8</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>N=3 n=161; 0.5% vs. 0.8%, OR=0.33, 95%CI: 0.02, 6.09</t>
+          <t>N=3 n=161; 0.3% vs. 0.8%, OR=0.33, 95%CI: 0.02, 6.09</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>N=7 n=1451; Random-effects: 9.8% vs. 6.1%, OR=1.57, 95%CI: 0.94, 2.61; Fixed-effecs: OR=1.62, 95%CI: 1.06, 2.47</t>
+          <t>N=7 n=1451; Random-effects: 9.3% vs. 6.1%, OR=1.57, 95%CI: 0.94, 2.61; Fixed-effecs: OR=1.62, 95%CI: 1.06, 2.47</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1411,7 +1411,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>N=7 n=1451; Random-effects: 6.3% vs. 2.8%, OR=2.05, 95%CI: 1.08, 3.91; Fixed-effecs: OR=2.17, 95%CI: 1.2, 3.91</t>
+          <t>N=7 n=1451; Random-effects: 5.6% vs. 2.8%, OR=2.05, 95%CI: 1.08, 3.91; Fixed-effecs: OR=2.17, 95%CI: 1.2, 3.91</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1552,7 +1552,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>N=3 n=161; Random-effects: 19.7% vs. 0.8%, OR=15.34, 95%CI: 3.74, 62.92; Fixed-effecs: OR=15.34, 95%CI: 3.74, 62.92</t>
+          <t>N=3 n=161; Random-effects: 10.9% vs. 0.8%, OR=15.34, 95%CI: 3.74, 62.92; Fixed-effecs: OR=15.34, 95%CI: 3.74, 62.92</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1599,7 +1599,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>N=7 n=1451; Random-effects: 5.6% vs. 3.7%, OR=1.24, 95%CI: 0.61, 2.53; Fixed-effecs: OR=1.32, 95%CI: 0.79, 2.21</t>
+          <t>N=7 n=1451; Random-effects: 4.5% vs. 3.7%, OR=1.24, 95%CI: 0.61, 2.53; Fixed-effecs: OR=1.32, 95%CI: 0.79, 2.21</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1928,7 +1928,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>N=5 n=1385; Random-effects: 5.5% vs. 4.5%, OR=1.19, 95%CI: 0.71, 1.99; Fixed-effecs: OR=1.22, 95%CI: 0.73, 2.04</t>
+          <t>N=5 n=1385; Random-effects: 5.3% vs. 4.5%, OR=1.19, 95%CI: 0.71, 1.99; Fixed-effecs: OR=1.22, 95%CI: 0.73, 2.04</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -2022,7 +2022,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>N=5 n=1385; Random-effects: 5.2% vs. 5.5%, OR=0.89, 95%CI: 0.3, 2.64; Fixed-effecs: OR=1.17, 95%CI: 0.73, 1.89</t>
+          <t>N=5 n=1385; Random-effects: 4.9% vs. 5.5%, OR=0.89, 95%CI: 0.3, 2.64; Fixed-effecs: OR=1.17, 95%CI: 0.73, 1.89</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -2069,7 +2069,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>N=3 n=161; Random-effects: 28.9% vs. 0.6%, OR=9.6, 95%CI: 3.51, 26.27; Fixed-effecs: OR=9.6, 95%CI: 3.51, 26.27</t>
+          <t>N=3 n=161; Random-effects: 5.6% vs. 0.6%, OR=9.6, 95%CI: 3.51, 26.27; Fixed-effecs: OR=9.6, 95%CI: 3.51, 26.27</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -2116,7 +2116,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>N=5 n=774; Random-effects: 5.5% vs. 1.4%, OR=1.18, 95%CI: 0.47, 2.99; Fixed-effecs: OR=1.24, 95%CI: 0.48, 3.18</t>
+          <t>N=5 n=774; Random-effects: 1.6% vs. 1.4%, OR=1.18, 95%CI: 0.47, 2.99; Fixed-effecs: OR=1.24, 95%CI: 0.48, 3.18</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -2163,7 +2163,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>N=7 n=1451; Random-effects: 8.5% vs. 6.5%, OR=1.16, 95%CI: 0.47, 2.84; Fixed-effecs: OR=1.15, 95%CI: 0.75, 1.76</t>
+          <t>N=7 n=1451; Random-effects: 7.4% vs. 6.5%, OR=1.16, 95%CI: 0.47, 2.84; Fixed-effecs: OR=1.15, 95%CI: 0.75, 1.76</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -2257,7 +2257,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>N=6 n=1412; Random-effects: 10.7% vs. 8.2%, OR=1.29, 95%CI: 0.86, 1.95; Fixed-effecs: OR=1.32, 95%CI: 0.89, 1.94</t>
+          <t>N=6 n=1412; Random-effects: 10.3% vs. 8.2%, OR=1.29, 95%CI: 0.86, 1.95; Fixed-effecs: OR=1.32, 95%CI: 0.89, 1.94</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>N=2 n=92; 8.1% vs. 1.1%, OR=5.32, 95%CI: 0.6, 46.78</t>
+          <t>N=2 n=92; 5.5% vs. 1.1%, OR=5.32, 95%CI: 0.6, 46.78</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -2492,7 +2492,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>N=2 n=137; Random-effects: 19.9% vs. 2.9%, OR=6.89, 95%CI: 1.98, 23.92; Fixed-effecs: OR=6.89, 95%CI: 1.98, 23.92</t>
+          <t>N=2 n=137; Random-effects: 17.3% vs. 2.9%, OR=6.89, 95%CI: 1.98, 23.92; Fixed-effecs: OR=6.89, 95%CI: 1.98, 23.92</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2539,7 +2539,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>N=4 n=529; Random-effects: 6.2% vs. 0.3%, OR=2.23, 95%CI: 0.34, 14.68; Fixed-effecs: OR=3.14, 95%CI: 0.33, 29.62</t>
+          <t>N=4 n=529; Random-effects: 0.8% vs. 0.3%, OR=2.23, 95%CI: 0.34, 14.68; Fixed-effecs: OR=3.14, 95%CI: 0.33, 29.62</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2633,7 +2633,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>N=3 n=490; Random-effects: 3.3% vs. 0.4%, OR=1.28, 95%CI: 0.15, 11.23; Fixed-effecs: OR=1.44, 95%CI: 0.14, 15.03</t>
+          <t>N=3 n=490; Random-effects: 0.5% vs. 0.4%, OR=1.28, 95%CI: 0.15, 11.23; Fixed-effecs: OR=1.44, 95%CI: 0.14, 15.03</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2680,7 +2680,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>N=7 n=1451; Random-effects: 9.3% vs. 5.2%, OR=1.76, 95%CI: 0.92, 3.37; Fixed-effecs: OR=2.01, 95%CI: 1.29, 3.14</t>
+          <t>N=7 n=1451; Random-effects: 8.8% vs. 5.2%, OR=1.76, 95%CI: 0.92, 3.37; Fixed-effecs: OR=2.01, 95%CI: 1.29, 3.14</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -4325,7 +4325,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>N=2 n=102; Random-effects: 42.4% vs. 8.7%, OR=7.78, 95%CI: 2.83, 21.4; Fixed-effecs: OR=7.78, 95%CI: 2.83, 21.4</t>
+          <t>N=2 n=102; Random-effects: 42.5% vs. 8.7%, OR=7.78, 95%CI: 2.83, 21.4; Fixed-effecs: OR=7.78, 95%CI: 2.83, 21.4</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -4701,7 +4701,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>N=2 n=102; Random-effects: 22.7% vs. 1.5%, OR=12.5, 95%CI: 2.33, 67.21; Fixed-effecs: OR=12.5, 95%CI: 2.33, 67.21</t>
+          <t>N=2 n=102; Random-effects: 15.9% vs. 1.5%, OR=12.5, 95%CI: 2.33, 67.21; Fixed-effecs: OR=12.5, 95%CI: 2.33, 67.21</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">

--- a/data_u1/meta_outcome_soe.xlsx
+++ b/data_u1/meta_outcome_soe.xlsx
@@ -481,7 +481,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>80% of eligible studies and 94.3% of participants had usable data.</t>
+          <t>80% of eligible studies and 94.2% of participants had usable data.</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -1139,7 +1139,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>77.8% of eligible studies and 91.1% of participants had usable data.</t>
+          <t>77.8% of eligible studies and 91% of participants had usable data.</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1233,7 +1233,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>77.8% of eligible studies and 91.1% of participants had usable data.</t>
+          <t>77.8% of eligible studies and 91% of participants had usable data.</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1327,7 +1327,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>77.8% of eligible studies and 91.1% of participants had usable data.</t>
+          <t>77.8% of eligible studies and 91% of participants had usable data.</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1421,7 +1421,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>77.8% of eligible studies and 91.1% of participants had usable data.</t>
+          <t>77.8% of eligible studies and 91% of participants had usable data.</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1515,7 +1515,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>77.8% of eligible studies and 91.1% of participants had usable data.</t>
+          <t>77.8% of eligible studies and 91% of participants had usable data.</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1609,7 +1609,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>77.8% of eligible studies and 91.1% of participants had usable data.</t>
+          <t>77.8% of eligible studies and 91% of participants had usable data.</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -1703,7 +1703,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>22.2% of eligible studies and 28.8% of participants had usable data.</t>
+          <t>22.2% of eligible studies and 28.7% of participants had usable data.</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2173,7 +2173,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>77.8% of eligible studies and 91.1% of participants had usable data.</t>
+          <t>77.8% of eligible studies and 91% of participants had usable data.</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2643,7 +2643,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>33.3% of eligible studies and 30.8% of participants had usable data.</t>
+          <t>33.3% of eligible studies and 30.7% of participants had usable data.</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -2690,7 +2690,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>77.8% of eligible studies and 91.1% of participants had usable data.</t>
+          <t>77.8% of eligible studies and 91% of participants had usable data.</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
